--- a/docs/design/ACSMS-SCR-015/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者販売店一括置換画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-015/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者販売店一括置換画面_V1.0.xlsx
@@ -1354,7 +1354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG5"/>
+  <dimension ref="A1:AG7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -1691,19 +1691,146 @@
       <c r="AF5" s="10" t="n"/>
       <c r="AG5" s="11" t="n"/>
     </row>
+    <row r="6" ht="19.5" customHeight="1">
+      <c r="A6" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>2026/07/22</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I6" s="10" t="n"/>
+      <c r="J6" s="11" t="n"/>
+      <c r="K6" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="n"/>
+      <c r="M6" s="10" t="n"/>
+      <c r="N6" s="10" t="n"/>
+      <c r="O6" s="10" t="n"/>
+      <c r="P6" s="10" t="n"/>
+      <c r="Q6" s="11" t="n"/>
+      <c r="R6" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件（2026-07 改訂）：**電子版(2) を本画面（販売店一括置換）の対象外**に変更。検索・置換実行 両 API とも `dokusya_shubetsu=2` は日付に関係なく HTTP 400 (`VALIDATION_ERROR`, `{ field: "dokusya_shubetsu", message: "電子版は本画面では対象外です。" }`／ACSMS-MSG-015-009) を返す（候補取得より前に拒否・FE の検索ボタン無効化に対する防御的ガード）。電子版=電子配信で販売店を持たないため一括置換できない。※1.3 の「電子版=当日置換」は撤回。</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="n"/>
+      <c r="T6" s="10" t="n"/>
+      <c r="U6" s="10" t="n"/>
+      <c r="V6" s="11" t="n"/>
+      <c r="W6" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X6" s="10" t="n"/>
+      <c r="Y6" s="10" t="n"/>
+      <c r="Z6" s="10" t="n"/>
+      <c r="AA6" s="11" t="n"/>
+      <c r="AB6" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC6" s="10" t="n"/>
+      <c r="AD6" s="10" t="n"/>
+      <c r="AE6" s="10" t="n"/>
+      <c r="AF6" s="10" t="n"/>
+      <c r="AG6" s="11" t="n"/>
+    </row>
+    <row r="7" ht="19.5" customHeight="1">
+      <c r="A7" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="n"/>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>2026/07/23</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I7" s="10" t="n"/>
+      <c r="J7" s="11" t="n"/>
+      <c r="K7" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="n"/>
+      <c r="M7" s="10" t="n"/>
+      <c r="N7" s="10" t="n"/>
+      <c r="O7" s="10" t="n"/>
+      <c r="P7" s="10" t="n"/>
+      <c r="Q7" s="11" t="n"/>
+      <c r="R7" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件（2026-07）：`t_dokusya_rireki.hanbaiten_tekiyo_date`（販売店適用日）カラムを廃止。検索・置換実行 両 API のリクエスト項目 `hanbaiten_tekiyo_date` を `joho_henko_tekiyo_date`（適用日）へ改名し、適用日を読者情報変更適用日に一本化（販売店のみ変更でも同一適用日で履歴1件・専用の販売店適用日列は持たない）。</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="n"/>
+      <c r="T7" s="10" t="n"/>
+      <c r="U7" s="10" t="n"/>
+      <c r="V7" s="11" t="n"/>
+      <c r="W7" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X7" s="10" t="n"/>
+      <c r="Y7" s="10" t="n"/>
+      <c r="Z7" s="10" t="n"/>
+      <c r="AA7" s="11" t="n"/>
+      <c r="AB7" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC7" s="10" t="n"/>
+      <c r="AD7" s="10" t="n"/>
+      <c r="AE7" s="10" t="n"/>
+      <c r="AF7" s="10" t="n"/>
+      <c r="AG7" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="49">
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="AB1:AG1"/>
+    <mergeCell ref="C6:G6"/>
     <mergeCell ref="R5:V5"/>
+    <mergeCell ref="W6:AA6"/>
     <mergeCell ref="C5:G5"/>
+    <mergeCell ref="K7:Q7"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="W5:AA5"/>
     <mergeCell ref="R4:V4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="H7:J7"/>
     <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="C4:G4"/>
+    <mergeCell ref="R7:V7"/>
     <mergeCell ref="K4:Q4"/>
+    <mergeCell ref="K6:Q6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="R6:V6"/>
     <mergeCell ref="C1:G1"/>
     <mergeCell ref="K3:Q3"/>
     <mergeCell ref="W4:AA4"/>
@@ -1711,16 +1838,20 @@
     <mergeCell ref="W3:AA3"/>
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="AB7:AG7"/>
     <mergeCell ref="K5:Q5"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="W7:AA7"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H5:J5"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="R3:V3"/>
     <mergeCell ref="AB3:AG3"/>
     <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="AB6:AG6"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C7:G7"/>
     <mergeCell ref="AB5:AG5"/>
     <mergeCell ref="W2:AA2"/>
     <mergeCell ref="H4:J4"/>
@@ -1728,6 +1859,7 @@
     <mergeCell ref="AB4:AG4"/>
     <mergeCell ref="K2:Q2"/>
     <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H6:J6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1900,7 +2032,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/18</t>
+          <t>2026/07/23</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2416,7 +2548,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/18</t>
+          <t>2026/07/23</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3345,7 +3477,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/18</t>
+          <t>2026/07/23</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3490,7 +3622,7 @@
       <c r="R6" s="11" t="n"/>
       <c r="S6" s="19" t="inlineStr">
         <is>
-          <t>販売店一括置換対象の購読者を検索する（検索条件 + DataScope + ページネーション対応）。`tetsuzuki_shurui=1`（購読中）のみ返却。`hanbaiten_tekiyo_date`（販売店適用日）は**必須**で、その適用日時点で置換可能な購読者のみ返却する（顧客要件 2026-07：画面初期表示では検索しない・適用日を入力して検索する運用）。</t>
+          <t>販売店一括置換対象の購読者を検索する（検索条件 + DataScope + ページネーション対応）。`tetsuzuki_shurui=1`（購読中）のみ返却。`joho_henko_tekiyo_date`（適用日）は**必須**で、その適用日時点で置換可能な購読者のみ返却する（顧客要件 2026-07：画面初期表示では検索しない・適用日を入力して検索する運用）。</t>
         </is>
       </c>
       <c r="T6" s="10" t="n"/>
@@ -3906,7 +4038,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/18</t>
+          <t>2026/07/23</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -4030,7 +4162,7 @@
       <c r="I8" s="11" t="n"/>
       <c r="J8" s="19" t="inlineStr">
         <is>
-          <t>販売店一括置換対象の購読者を検索する（検索条件 + DataScope + ページネーション対応）。`tetsuzuki_shurui=1`（購読中）のみ返却。`hanbaiten_tekiyo_date`（販売店適用日）は**必須**で、その適用日時点で置換可能な購読者のみ返却する（顧客要件 2026-07：画面初期表示では検索しない・適用日を入力して検索する運用）。</t>
+          <t>販売店一括置換対象の購読者を検索する（検索条件 + DataScope + ページネーション対応）。`tetsuzuki_shurui=1`（購読中）のみ返却。`joho_henko_tekiyo_date`（適用日）は**必須**で、その適用日時点で置換可能な購読者のみ返却する（顧客要件 2026-07：画面初期表示では検索しない・適用日を入力して検索する運用）。</t>
         </is>
       </c>
       <c r="K8" s="10" t="n"/>
@@ -5140,13 +5272,13 @@
       <c r="AJ31" s="10" t="n"/>
       <c r="AK31" s="11" t="n"/>
     </row>
-    <row r="32" ht="72" customHeight="1">
+    <row r="32" ht="54" customHeight="1">
       <c r="B32" s="31" t="n">
         <v>10</v>
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>hanbaiten_tekiyo_date</t>
+          <t>joho_henko_tekiyo_date</t>
         </is>
       </c>
       <c r="D32" s="10" t="n"/>
@@ -5193,7 +5325,7 @@
       <c r="AE32" s="11" t="n"/>
       <c r="AF32" s="19" t="inlineStr">
         <is>
-          <t>販売店適用日 YYYY-MM-DD。**必須**。適用日ルールは `dokusya_shubetsu` 依存（顧客要件 2026-07 改訂）：**紙版=未来日のみ（`&gt; 当日`）／電子版=当日のみ（`= 当日`）**。この適用日時点で置換可能な購読者のみ返却する（後述 §置換可能条件）。置換実行 API の適用日と同一基準</t>
+          <t>適用日 YYYY-MM-DD。**必須**。**紙版=未来日のみ（`&gt; 当日`）**（顧客要件 2026-07 改訂）。この適用日時点で置換可能な購読者のみ返却する（後述 §置換可能条件）。置換実行 API の適用日と同一基準</t>
         </is>
       </c>
       <c r="AG32" s="10" t="n"/>
@@ -5202,7 +5334,7 @@
       <c r="AJ32" s="10" t="n"/>
       <c r="AK32" s="11" t="n"/>
     </row>
-    <row r="33" ht="72" customHeight="1">
+    <row r="33" ht="90" customHeight="1">
       <c r="B33" s="31" t="n">
         <v>11</v>
       </c>
@@ -5257,7 +5389,7 @@
       <c r="AE33" s="11" t="n"/>
       <c r="AF33" s="19" t="inlineStr">
         <is>
-          <t>購読種別（**必須・1:紙版 / 2:電子版 のみ**。3:併読 は対象外・顧客要件 2026-07）。この種別で購読者を絞り込む（`d.dokusya_shubetsu = :dokusya_shubetsu`）。適用日ルール（紙版=未来 / 電子版=当日）の判定にも用いる</t>
+          <t>購読種別（**必須・1:紙版 / 2:電子版**。3:併読 は対象外）。この種別で購読者を絞り込む（`d.dokusya_shubetsu = :dokusya_shubetsu`）。**電子版(2) は本画面の対象外** → 日付に関係なく `VALIDATION_ERROR`（`電子版は本画面では対象外です。`／ACSMS-MSG-015-009・顧客要件 2026-07 改訂）</t>
         </is>
       </c>
       <c r="AG33" s="10" t="n"/>
@@ -6728,7 +6860,7 @@
     <row r="64" ht="18" customHeight="1">
       <c r="C64" s="19" t="inlineStr">
         <is>
-          <t>GET /api/v1/dokusya/replace-hanbaiten/search?hanbaiten_tekiyo_date=2026-08-01&amp;kanri_shiten_id=10&amp;kumiaiin_code=10001&amp;page=1&amp;per_page=20&amp;sort_by=kumiaiin_code&amp;sort_order=asc</t>
+          <t>GET /api/v1/dokusya/replace-hanbaiten/search?joho_henko_tekiyo_date=2026-08-01&amp;kanri_shiten_id=10&amp;kumiaiin_code=10001&amp;page=1&amp;per_page=20&amp;sort_by=kumiaiin_code&amp;sort_order=asc</t>
         </is>
       </c>
       <c r="D64" s="10" t="n"/>
@@ -7306,7 +7438,7 @@
     <row r="112" ht="90" customHeight="1">
       <c r="C112" s="41" t="inlineStr">
         <is>
-          <t>**入力チェック（適用日・種別依存／顧客要件 2026-07 改訂）**：`hanbaiten_tekiyo_date` は必須。未入力は HTTP 400 (`VALIDATION_ERROR`, `適用日を入力してください。`)、形式（YYYY-MM-DD）不正も 400。日付ルールは `dokusya_shubetsu` 依存で判定する（当日判定は `todayIsoJst()` = Asia/Tokyo、置換実行 API と同一基準）：</t>
+          <t>**入力チェック（適用日・種別依存／顧客要件 2026-07 改訂）**：`joho_henko_tekiyo_date` は必須。未入力は HTTP 400 (`VALIDATION_ERROR`, `適用日を入力してください。`)、形式（YYYY-MM-DD）不正も 400。日付ルールは `dokusya_shubetsu` 依存で判定する（当日判定は `todayIsoJst()` = Asia/Tokyo、置換実行 API と同一基準）：</t>
         </is>
       </c>
     </row>
@@ -7317,10 +7449,10 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="54" customHeight="1">
+    <row r="114" ht="108" customHeight="1">
       <c r="D114" s="41" t="inlineStr">
         <is>
-          <t>**電子版(2)**：**当日のみ**（`= 当日`）。当日以外は HTTP 400 (`DATE_RANGE_INVALID`, `電子版の適用日は本日を指定してください。`)。UI は電子版選択時に適用日を当日へ自動セットしピッカーを非活性化する。</t>
+          <t>**電子版(2)**：**本画面（販売店一括置換）の対象外**。日付に関係なく HTTP 400 (`VALIDATION_ERROR`, `{ field: "dokusya_shubetsu", message: "電子版は本画面では対象外です。" }`／ACSMS-MSG-015-009)。電子版=電子配信で販売店を持たないため一括置換できない（顧客要件 2026-07 改訂で「電子版=当日置換」を撤回）。UI は電子版選択時にトーストでこのメッセージを通知し検索ボタンを非活性化する（インラインメッセージは表示しない）。</t>
         </is>
       </c>
     </row>
@@ -7348,21 +7480,21 @@
     <row r="118" ht="72" customHeight="1">
       <c r="C118" s="41" t="inlineStr">
         <is>
-          <t>**置換可能条件（顧客要件 2026-07）**：指定した `hanbaiten_tekiyo_date`（販売店適用日）時点で置換可能な購読者のみに絞り込む。置換実行 API の集約チェック（`assertReplaceTekiyoDate`）と同一境界を per-row で適用するため、返却された任意の部分集合を選択しても実行時チェックが必ず通る：</t>
+          <t>**置換可能条件（顧客要件 2026-07）**：指定した `joho_henko_tekiyo_date`（適用日）時点で置換可能な購読者のみに絞り込む。置換実行 API の集約チェック（`assertReplaceTekiyoDate`）と同一境界を per-row で適用するため、返却された任意の部分集合を選択しても実行時チェックが必ず通る：</t>
         </is>
       </c>
     </row>
     <row r="119" ht="36" customHeight="1">
       <c r="D119" s="41" t="inlineStr">
         <is>
-          <t>`d.dokusya_kaishi_date &lt;= :hanbaiten_tekiyo_date`（購読開始日が適用日以前）</t>
+          <t>`d.dokusya_kaishi_date &lt;= :joho_henko_tekiyo_date`（購読開始日が適用日以前）</t>
         </is>
       </c>
     </row>
     <row r="120" ht="54" customHeight="1">
       <c r="D120" s="41" t="inlineStr">
         <is>
-          <t>`(d.dokusya_chushi_date IS NULL OR d.dokusya_chushi_date &gt; :hanbaiten_tekiyo_date)`（解約予定日が無い、または適用日より後）</t>
+          <t>`(d.dokusya_chushi_date IS NULL OR d.dokusya_chushi_date &gt; :joho_henko_tekiyo_date)`（解約予定日が無い、または適用日より後）</t>
         </is>
       </c>
     </row>
@@ -7460,14 +7592,14 @@
     <row r="134" ht="36" customHeight="1">
       <c r="D134" s="41" t="inlineStr">
         <is>
-          <t>`d.dokusya_kaishi_date &lt;= :hanbaiten_tekiyo_date`（置換可能条件）</t>
+          <t>`d.dokusya_kaishi_date &lt;= :joho_henko_tekiyo_date`（置換可能条件）</t>
         </is>
       </c>
     </row>
     <row r="135" ht="36" customHeight="1">
       <c r="D135" s="41" t="inlineStr">
         <is>
-          <t>`(d.dokusya_chushi_date IS NULL OR d.dokusya_chushi_date &gt; :hanbaiten_tekiyo_date)`（置換可能条件）</t>
+          <t>`(d.dokusya_chushi_date IS NULL OR d.dokusya_chushi_date &gt; :joho_henko_tekiyo_date)`（置換可能条件）</t>
         </is>
       </c>
     </row>
@@ -7487,8 +7619,8 @@
 WHERE d.tetsuzuki_shurui = 1
   AND d.deleted_at IS NULL
   /* 置換可能条件（適用日時点で置換可能な購読者のみ） */
-  AND d.dokusya_kaishi_date &lt;= :hanbaiten_tekiyo_date
-  AND (d.dokusya_chushi_date IS NULL OR d.dokusya_chushi_date &gt; :hanbaiten_tekiyo_date)
+  AND d.dokusya_kaishi_date &lt;= :joho_henko_tekiyo_date
+  AND (d.dokusya_chushi_date IS NULL OR d.dokusya_chushi_date &gt; :joho_henko_tekiyo_date)
   /* DataScope: JA_KANRI_SHITEN */
   AND d.kanri_shiten_id = :user_kanri_shiten_id
   /* DataScope: JA_HONTEN / CHUOKAI */
@@ -8178,7 +8310,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/18</t>
+          <t>2026/07/23</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -9070,13 +9202,13 @@
       <c r="AJ26" s="10" t="n"/>
       <c r="AK26" s="11" t="n"/>
     </row>
-    <row r="27" ht="36" customHeight="1">
+    <row r="27" ht="18" customHeight="1">
       <c r="B27" s="31" t="n">
         <v>4</v>
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>hanbaiten_tekiyo_date</t>
+          <t>joho_henko_tekiyo_date</t>
         </is>
       </c>
       <c r="D27" s="10" t="n"/>
@@ -9123,7 +9255,7 @@
       <c r="AE27" s="11" t="n"/>
       <c r="AF27" s="19" t="inlineStr">
         <is>
-          <t>販売店適用日（YYYY-MM-DD）。適用日ルールは `dokusya_shubetsu` 依存：紙版=未来日のみ／電子版=当日のみ（顧客要件 2026-07 改訂）</t>
+          <t>適用日（YYYY-MM-DD）。**紙版=未来日のみ**（顧客要件 2026-07 改訂）</t>
         </is>
       </c>
       <c r="AG27" s="10" t="n"/>
@@ -9132,7 +9264,7 @@
       <c r="AJ27" s="10" t="n"/>
       <c r="AK27" s="11" t="n"/>
     </row>
-    <row r="28" ht="36" customHeight="1">
+    <row r="28" ht="72" customHeight="1">
       <c r="B28" s="31" t="n">
         <v>5</v>
       </c>
@@ -9187,7 +9319,7 @@
       <c r="AE28" s="11" t="n"/>
       <c r="AF28" s="19" t="inlineStr">
         <is>
-          <t>購読種別（**必須・1:紙版 / 2:電子版 のみ**）。適用日ルール判定 + 全候補が同一種別であることの整合チェックに用いる（顧客要件 2026-07）</t>
+          <t>購読種別（**必須・1:紙版 / 2:電子版**）。全候補が同一種別であることの整合チェックに用いる。**電子版(2) は本画面の対象外** → `VALIDATION_ERROR`（`電子版は本画面では対象外です。`／ACSMS-MSG-015-009・顧客要件 2026-07 改訂）</t>
         </is>
       </c>
       <c r="AG28" s="10" t="n"/>
@@ -9683,7 +9815,7 @@
 {
   "dokusya_ids": [5001, 5002, 5003],
   "new_hanbaiten_id": 201,
-  "hanbaiten_tekiyo_date": "2026-06-01"
+  "joho_henko_tekiyo_date": "2026-06-01"
 }</t>
         </is>
       </c>
@@ -9794,7 +9926,7 @@
   "message": "入力値が不正です。詳細はerrorsフィールドを確認してください。",
   "errors": [
     { "field": "new_hanbaiten_id", "message": "必須項目です。" },
-    { "field": "hanbaiten_tekiyo_date", "message": "必須項目です。" }
+    { "field": "joho_henko_tekiyo_date", "message": "必須項目です。" }
   ]
 }</t>
         </is>
@@ -10282,99 +10414,106 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="90" customHeight="1">
+    <row r="79" ht="72" customHeight="1">
       <c r="D79" s="41" t="inlineStr">
         <is>
-          <t>hanbaiten_tekiyo_date：必須、YYYY-MM-DD 形式。**種別依存の日付ルール**（顧客要件 2026-07 改訂）：紙版=未来日のみ（`&gt; 当日`、`DATE_RANGE_INVALID` `紙版の適用日は本日より後の日付を入力してください。`）／電子版=当日のみ（`= 当日`、`DATE_RANGE_INVALID` `電子版の適用日は本日を指定してください。`）。当日判定は `todayIsoJst()`（Asia/Tokyo）</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="90" customHeight="1">
-      <c r="C80" s="41" t="inlineStr">
+          <t>dokusya_shubetsu：**電子版(2) は本画面の対象外** → 日付に関係なく HTTP 400 (`VALIDATION_ERROR`, `{ field: "dokusya_shubetsu", message: "電子版は本画面では対象外です。" }`／ACSMS-MSG-015-009・顧客要件 2026-07 改訂)。候補取得(find)より前に拒否する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="54" customHeight="1">
+      <c r="D80" s="41" t="inlineStr">
+        <is>
+          <t>joho_henko_tekiyo_date：必須、YYYY-MM-DD 形式。**紙版=未来日のみ**（`&gt; 当日`、`DATE_RANGE_INVALID` `紙版の適用日は本日より後の日付を入力してください。`）。当日判定は `todayIsoJst()`（Asia/Tokyo）</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="90" customHeight="1">
+      <c r="C81" s="41" t="inlineStr">
         <is>
           <t>**候補種別の整合チェック（顧客要件 2026-07）**：選択された全候補の `dokusya_shubetsu` が指定の `dokusya_shubetsu` と一致すること（検索で種別絞り込み済みだが、id 改竄・不整合を防ぐ防御）。不一致は HTTP 400 (`DATE_RANGE_INVALID`, `選択した購読者に指定の購読種別と異なる購読者が含まれています。`)。併読・電子版クレカは従来どおり ineligible（4.3）</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="C81" s="41" t="inlineStr">
+    <row r="82" ht="18" customHeight="1">
+      <c r="C82" s="41" t="inlineStr">
         <is>
           <t>不正な場合：HTTP 400 (`VALIDATION_ERROR`)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="B82" s="27" t="inlineStr">
+    <row r="83" ht="18" customHeight="1">
+      <c r="B83" s="27" t="inlineStr">
         <is>
           <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="C83" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="C84" s="41" t="inlineStr">
         <is>
-          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="C85" s="41" t="inlineStr">
         <is>
+          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="C86" s="41" t="inlineStr">
+        <is>
           <t>必要権限: `dokusya.replace_hanbaiten`</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="36" customHeight="1">
-      <c r="C86" s="41" t="inlineStr">
+    <row r="87" ht="36" customHeight="1">
+      <c r="C87" s="41" t="inlineStr">
         <is>
           <t>該当権限保持ロール: CHUOKAI（中央会）/ JA_HONTEN（JA本店）/ JA_KANRI_SHITEN（JA管理支店）</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="C87" s="41" t="inlineStr">
+    <row r="88" ht="18" customHeight="1">
+      <c r="C88" s="41" t="inlineStr">
         <is>
           <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="36" customHeight="1">
-      <c r="C88" s="41" t="inlineStr">
-        <is>
-          <t>DataScope: ログインユーザーの `ja_id`（および JA_KANRI_SHITEN の場合は `kanri_shiten_id`）を取得する。</t>
         </is>
       </c>
     </row>
     <row r="89" ht="36" customHeight="1">
       <c r="C89" s="41" t="inlineStr">
         <is>
+          <t>DataScope: ログインユーザーの `ja_id`（および JA_KANRI_SHITEN の場合は `kanri_shiten_id`）を取得する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="36" customHeight="1">
+      <c r="C90" s="41" t="inlineStr">
+        <is>
           <t>DataScope違反（他JA・他管理支店のレコードへのアクセス）の場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="18" customHeight="1">
-      <c r="B90" s="27" t="inlineStr">
+    <row r="91" ht="18" customHeight="1">
+      <c r="B91" s="27" t="inlineStr">
         <is>
           <t>4.3 事前チェック（対象購読者の取得と検証）</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="18" customHeight="1">
-      <c r="C91" s="41" t="inlineStr">
+    <row r="92" ht="18" customHeight="1">
+      <c r="C92" s="41" t="inlineStr">
         <is>
           <t>対象購読者を取得し、DataScope と業務ルールを検証する。</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="108" customHeight="1">
-      <c r="C92" s="42" t="inlineStr">
+    <row r="93" ht="108" customHeight="1">
+      <c r="C93" s="42" t="inlineStr">
         <is>
           <t>SELECT dokusya_id, ja_id, kanri_shiten_id, hanbaiten_id,
        dokusya_shubetsu, shiharai_hoho, rireki_no
@@ -10384,85 +10523,85 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D92" s="10" t="n"/>
-      <c r="E92" s="10" t="n"/>
-      <c r="F92" s="10" t="n"/>
-      <c r="G92" s="10" t="n"/>
-      <c r="H92" s="10" t="n"/>
-      <c r="I92" s="10" t="n"/>
-      <c r="J92" s="10" t="n"/>
-      <c r="K92" s="10" t="n"/>
-      <c r="L92" s="10" t="n"/>
-      <c r="M92" s="10" t="n"/>
-      <c r="N92" s="10" t="n"/>
-      <c r="O92" s="10" t="n"/>
-      <c r="P92" s="10" t="n"/>
-      <c r="Q92" s="10" t="n"/>
-      <c r="R92" s="10" t="n"/>
-      <c r="S92" s="10" t="n"/>
-      <c r="T92" s="10" t="n"/>
-      <c r="U92" s="10" t="n"/>
-      <c r="V92" s="10" t="n"/>
-      <c r="W92" s="10" t="n"/>
-      <c r="X92" s="10" t="n"/>
-      <c r="Y92" s="10" t="n"/>
-      <c r="Z92" s="10" t="n"/>
-      <c r="AA92" s="10" t="n"/>
-      <c r="AB92" s="10" t="n"/>
-      <c r="AC92" s="10" t="n"/>
-      <c r="AD92" s="10" t="n"/>
-      <c r="AE92" s="10" t="n"/>
-      <c r="AF92" s="10" t="n"/>
-      <c r="AG92" s="10" t="n"/>
-      <c r="AH92" s="10" t="n"/>
-      <c r="AI92" s="10" t="n"/>
-      <c r="AJ92" s="10" t="n"/>
-      <c r="AK92" s="11" t="n"/>
-    </row>
-    <row r="93" ht="18" customHeight="1">
-      <c r="C93" s="41" t="inlineStr">
+      <c r="D93" s="10" t="n"/>
+      <c r="E93" s="10" t="n"/>
+      <c r="F93" s="10" t="n"/>
+      <c r="G93" s="10" t="n"/>
+      <c r="H93" s="10" t="n"/>
+      <c r="I93" s="10" t="n"/>
+      <c r="J93" s="10" t="n"/>
+      <c r="K93" s="10" t="n"/>
+      <c r="L93" s="10" t="n"/>
+      <c r="M93" s="10" t="n"/>
+      <c r="N93" s="10" t="n"/>
+      <c r="O93" s="10" t="n"/>
+      <c r="P93" s="10" t="n"/>
+      <c r="Q93" s="10" t="n"/>
+      <c r="R93" s="10" t="n"/>
+      <c r="S93" s="10" t="n"/>
+      <c r="T93" s="10" t="n"/>
+      <c r="U93" s="10" t="n"/>
+      <c r="V93" s="10" t="n"/>
+      <c r="W93" s="10" t="n"/>
+      <c r="X93" s="10" t="n"/>
+      <c r="Y93" s="10" t="n"/>
+      <c r="Z93" s="10" t="n"/>
+      <c r="AA93" s="10" t="n"/>
+      <c r="AB93" s="10" t="n"/>
+      <c r="AC93" s="10" t="n"/>
+      <c r="AD93" s="10" t="n"/>
+      <c r="AE93" s="10" t="n"/>
+      <c r="AF93" s="10" t="n"/>
+      <c r="AG93" s="10" t="n"/>
+      <c r="AH93" s="10" t="n"/>
+      <c r="AI93" s="10" t="n"/>
+      <c r="AJ93" s="10" t="n"/>
+      <c r="AK93" s="11" t="n"/>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="C94" s="41" t="inlineStr">
         <is>
           <t>ヒットしなかった `dokusya_id` がある場合：HTTP 404 (`NOT_FOUND`)</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="54" customHeight="1">
-      <c r="C94" s="41" t="inlineStr">
+    <row r="95" ht="54" customHeight="1">
+      <c r="C95" s="41" t="inlineStr">
         <is>
           <t>DataScope 違反（取得した行の `ja_id` / `kanri_shiten_id` がセッションのスコープと一致しない）の場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="C95" s="41" t="inlineStr">
+    <row r="96" ht="18" customHeight="1">
+      <c r="C96" s="41" t="inlineStr">
         <is>
           <t>業務ルールチェック：</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="36" customHeight="1">
-      <c r="D96" s="41" t="inlineStr">
+    <row r="97" ht="36" customHeight="1">
+      <c r="D97" s="41" t="inlineStr">
         <is>
           <t>いずれかの行で `hanbaiten_id = :new_hanbaiten_id` の場合：HTTP 400 (`SAME_HANBAITEN`)</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="72" customHeight="1">
-      <c r="D97" s="41" t="inlineStr">
+    <row r="98" ht="72" customHeight="1">
+      <c r="D98" s="41" t="inlineStr">
         <is>
           <t>いずれかの行で `dokusya_shubetsu = 3`（併読者）または（`dokusya_shubetsu = 2` かつ `shiharai_hoho = 6`：電子版クレカ決済）の場合：HTTP 400 (`INELIGIBLE_DOKUSYA`) + errors 配列（`dokusya_id` + `reason`）</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="18" customHeight="1">
-      <c r="B98" s="27" t="inlineStr">
+    <row r="99" ht="18" customHeight="1">
+      <c r="B99" s="27" t="inlineStr">
         <is>
           <t>4.4 置換先販売店の検証</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="72" customHeight="1">
-      <c r="C99" s="42" t="inlineStr">
+    <row r="100" ht="72" customHeight="1">
+      <c r="C100" s="42" t="inlineStr">
         <is>
           <t>SELECT hanbaiten_id, ja_id
 FROM m_hanbaiten
@@ -10470,75 +10609,75 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D99" s="10" t="n"/>
-      <c r="E99" s="10" t="n"/>
-      <c r="F99" s="10" t="n"/>
-      <c r="G99" s="10" t="n"/>
-      <c r="H99" s="10" t="n"/>
-      <c r="I99" s="10" t="n"/>
-      <c r="J99" s="10" t="n"/>
-      <c r="K99" s="10" t="n"/>
-      <c r="L99" s="10" t="n"/>
-      <c r="M99" s="10" t="n"/>
-      <c r="N99" s="10" t="n"/>
-      <c r="O99" s="10" t="n"/>
-      <c r="P99" s="10" t="n"/>
-      <c r="Q99" s="10" t="n"/>
-      <c r="R99" s="10" t="n"/>
-      <c r="S99" s="10" t="n"/>
-      <c r="T99" s="10" t="n"/>
-      <c r="U99" s="10" t="n"/>
-      <c r="V99" s="10" t="n"/>
-      <c r="W99" s="10" t="n"/>
-      <c r="X99" s="10" t="n"/>
-      <c r="Y99" s="10" t="n"/>
-      <c r="Z99" s="10" t="n"/>
-      <c r="AA99" s="10" t="n"/>
-      <c r="AB99" s="10" t="n"/>
-      <c r="AC99" s="10" t="n"/>
-      <c r="AD99" s="10" t="n"/>
-      <c r="AE99" s="10" t="n"/>
-      <c r="AF99" s="10" t="n"/>
-      <c r="AG99" s="10" t="n"/>
-      <c r="AH99" s="10" t="n"/>
-      <c r="AI99" s="10" t="n"/>
-      <c r="AJ99" s="10" t="n"/>
-      <c r="AK99" s="11" t="n"/>
-    </row>
-    <row r="100" ht="18" customHeight="1">
-      <c r="C100" s="41" t="inlineStr">
+      <c r="D100" s="10" t="n"/>
+      <c r="E100" s="10" t="n"/>
+      <c r="F100" s="10" t="n"/>
+      <c r="G100" s="10" t="n"/>
+      <c r="H100" s="10" t="n"/>
+      <c r="I100" s="10" t="n"/>
+      <c r="J100" s="10" t="n"/>
+      <c r="K100" s="10" t="n"/>
+      <c r="L100" s="10" t="n"/>
+      <c r="M100" s="10" t="n"/>
+      <c r="N100" s="10" t="n"/>
+      <c r="O100" s="10" t="n"/>
+      <c r="P100" s="10" t="n"/>
+      <c r="Q100" s="10" t="n"/>
+      <c r="R100" s="10" t="n"/>
+      <c r="S100" s="10" t="n"/>
+      <c r="T100" s="10" t="n"/>
+      <c r="U100" s="10" t="n"/>
+      <c r="V100" s="10" t="n"/>
+      <c r="W100" s="10" t="n"/>
+      <c r="X100" s="10" t="n"/>
+      <c r="Y100" s="10" t="n"/>
+      <c r="Z100" s="10" t="n"/>
+      <c r="AA100" s="10" t="n"/>
+      <c r="AB100" s="10" t="n"/>
+      <c r="AC100" s="10" t="n"/>
+      <c r="AD100" s="10" t="n"/>
+      <c r="AE100" s="10" t="n"/>
+      <c r="AF100" s="10" t="n"/>
+      <c r="AG100" s="10" t="n"/>
+      <c r="AH100" s="10" t="n"/>
+      <c r="AI100" s="10" t="n"/>
+      <c r="AJ100" s="10" t="n"/>
+      <c r="AK100" s="11" t="n"/>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="C101" s="41" t="inlineStr">
         <is>
           <t>未ヒット：HTTP 404 (`NOT_FOUND`)（販売店が存在しない）</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="36" customHeight="1">
-      <c r="C101" s="41" t="inlineStr">
+    <row r="102" ht="36" customHeight="1">
+      <c r="C102" s="41" t="inlineStr">
         <is>
           <t>`m_hanbaiten.ja_id` がセッションスコープと一致しない場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="18" customHeight="1">
-      <c r="B102" s="27" t="inlineStr">
+    <row r="103" ht="18" customHeight="1">
+      <c r="B103" s="27" t="inlineStr">
         <is>
           <t>4.5 データ更新（トランザクション）</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="18" customHeight="1">
-      <c r="C103" s="41" t="inlineStr">
+    <row r="104" ht="18" customHeight="1">
+      <c r="C104" s="41" t="inlineStr">
         <is>
           <t>DBトランザクションを開始する。</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="180" customHeight="1">
-      <c r="C104" s="42" t="inlineStr">
+    <row r="105" ht="180" customHeight="1">
+      <c r="C105" s="42" t="inlineStr">
         <is>
           <t>UPDATE t_dokusya
 SET hanbaiten_id = :new_hanbaiten_id,
-    joho_henko_tekiyo_date = :hanbaiten_tekiyo_date,  -- 顧客要件 2026-06: 販売店適用日に揃える
+    joho_henko_tekiyo_date = :joho_henko_tekiyo_date,  -- 顧客要件 2026-06: 適用日に揃える
     rireki_no = rireki_no + 1,
     updated_at = NOW(),
     updated_by = :user_account_id
@@ -10548,50 +10687,50 @@
 RETURNING dokusya_id, hanbaiten_id, rireki_no</t>
         </is>
       </c>
-      <c r="D104" s="10" t="n"/>
-      <c r="E104" s="10" t="n"/>
-      <c r="F104" s="10" t="n"/>
-      <c r="G104" s="10" t="n"/>
-      <c r="H104" s="10" t="n"/>
-      <c r="I104" s="10" t="n"/>
-      <c r="J104" s="10" t="n"/>
-      <c r="K104" s="10" t="n"/>
-      <c r="L104" s="10" t="n"/>
-      <c r="M104" s="10" t="n"/>
-      <c r="N104" s="10" t="n"/>
-      <c r="O104" s="10" t="n"/>
-      <c r="P104" s="10" t="n"/>
-      <c r="Q104" s="10" t="n"/>
-      <c r="R104" s="10" t="n"/>
-      <c r="S104" s="10" t="n"/>
-      <c r="T104" s="10" t="n"/>
-      <c r="U104" s="10" t="n"/>
-      <c r="V104" s="10" t="n"/>
-      <c r="W104" s="10" t="n"/>
-      <c r="X104" s="10" t="n"/>
-      <c r="Y104" s="10" t="n"/>
-      <c r="Z104" s="10" t="n"/>
-      <c r="AA104" s="10" t="n"/>
-      <c r="AB104" s="10" t="n"/>
-      <c r="AC104" s="10" t="n"/>
-      <c r="AD104" s="10" t="n"/>
-      <c r="AE104" s="10" t="n"/>
-      <c r="AF104" s="10" t="n"/>
-      <c r="AG104" s="10" t="n"/>
-      <c r="AH104" s="10" t="n"/>
-      <c r="AI104" s="10" t="n"/>
-      <c r="AJ104" s="10" t="n"/>
-      <c r="AK104" s="11" t="n"/>
-    </row>
-    <row r="105" ht="18" customHeight="1">
-      <c r="C105" s="41" t="inlineStr">
+      <c r="D105" s="10" t="n"/>
+      <c r="E105" s="10" t="n"/>
+      <c r="F105" s="10" t="n"/>
+      <c r="G105" s="10" t="n"/>
+      <c r="H105" s="10" t="n"/>
+      <c r="I105" s="10" t="n"/>
+      <c r="J105" s="10" t="n"/>
+      <c r="K105" s="10" t="n"/>
+      <c r="L105" s="10" t="n"/>
+      <c r="M105" s="10" t="n"/>
+      <c r="N105" s="10" t="n"/>
+      <c r="O105" s="10" t="n"/>
+      <c r="P105" s="10" t="n"/>
+      <c r="Q105" s="10" t="n"/>
+      <c r="R105" s="10" t="n"/>
+      <c r="S105" s="10" t="n"/>
+      <c r="T105" s="10" t="n"/>
+      <c r="U105" s="10" t="n"/>
+      <c r="V105" s="10" t="n"/>
+      <c r="W105" s="10" t="n"/>
+      <c r="X105" s="10" t="n"/>
+      <c r="Y105" s="10" t="n"/>
+      <c r="Z105" s="10" t="n"/>
+      <c r="AA105" s="10" t="n"/>
+      <c r="AB105" s="10" t="n"/>
+      <c r="AC105" s="10" t="n"/>
+      <c r="AD105" s="10" t="n"/>
+      <c r="AE105" s="10" t="n"/>
+      <c r="AF105" s="10" t="n"/>
+      <c r="AG105" s="10" t="n"/>
+      <c r="AH105" s="10" t="n"/>
+      <c r="AI105" s="10" t="n"/>
+      <c r="AJ105" s="10" t="n"/>
+      <c r="AK105" s="11" t="n"/>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="C106" s="41" t="inlineStr">
         <is>
           <t>既存履歴の `saishin_data_flg` を FALSE に更新：</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="72" customHeight="1">
-      <c r="C106" s="42" t="inlineStr">
+    <row r="107" ht="72" customHeight="1">
+      <c r="C107" s="42" t="inlineStr">
         <is>
           <t>UPDATE t_dokusya_rireki
 SET saishin_data_flg = FALSE
@@ -10599,50 +10738,50 @@
   AND saishin_data_flg = TRUE</t>
         </is>
       </c>
-      <c r="D106" s="10" t="n"/>
-      <c r="E106" s="10" t="n"/>
-      <c r="F106" s="10" t="n"/>
-      <c r="G106" s="10" t="n"/>
-      <c r="H106" s="10" t="n"/>
-      <c r="I106" s="10" t="n"/>
-      <c r="J106" s="10" t="n"/>
-      <c r="K106" s="10" t="n"/>
-      <c r="L106" s="10" t="n"/>
-      <c r="M106" s="10" t="n"/>
-      <c r="N106" s="10" t="n"/>
-      <c r="O106" s="10" t="n"/>
-      <c r="P106" s="10" t="n"/>
-      <c r="Q106" s="10" t="n"/>
-      <c r="R106" s="10" t="n"/>
-      <c r="S106" s="10" t="n"/>
-      <c r="T106" s="10" t="n"/>
-      <c r="U106" s="10" t="n"/>
-      <c r="V106" s="10" t="n"/>
-      <c r="W106" s="10" t="n"/>
-      <c r="X106" s="10" t="n"/>
-      <c r="Y106" s="10" t="n"/>
-      <c r="Z106" s="10" t="n"/>
-      <c r="AA106" s="10" t="n"/>
-      <c r="AB106" s="10" t="n"/>
-      <c r="AC106" s="10" t="n"/>
-      <c r="AD106" s="10" t="n"/>
-      <c r="AE106" s="10" t="n"/>
-      <c r="AF106" s="10" t="n"/>
-      <c r="AG106" s="10" t="n"/>
-      <c r="AH106" s="10" t="n"/>
-      <c r="AI106" s="10" t="n"/>
-      <c r="AJ106" s="10" t="n"/>
-      <c r="AK106" s="11" t="n"/>
-    </row>
-    <row r="107" ht="36" customHeight="1">
-      <c r="C107" s="41" t="inlineStr">
+      <c r="D107" s="10" t="n"/>
+      <c r="E107" s="10" t="n"/>
+      <c r="F107" s="10" t="n"/>
+      <c r="G107" s="10" t="n"/>
+      <c r="H107" s="10" t="n"/>
+      <c r="I107" s="10" t="n"/>
+      <c r="J107" s="10" t="n"/>
+      <c r="K107" s="10" t="n"/>
+      <c r="L107" s="10" t="n"/>
+      <c r="M107" s="10" t="n"/>
+      <c r="N107" s="10" t="n"/>
+      <c r="O107" s="10" t="n"/>
+      <c r="P107" s="10" t="n"/>
+      <c r="Q107" s="10" t="n"/>
+      <c r="R107" s="10" t="n"/>
+      <c r="S107" s="10" t="n"/>
+      <c r="T107" s="10" t="n"/>
+      <c r="U107" s="10" t="n"/>
+      <c r="V107" s="10" t="n"/>
+      <c r="W107" s="10" t="n"/>
+      <c r="X107" s="10" t="n"/>
+      <c r="Y107" s="10" t="n"/>
+      <c r="Z107" s="10" t="n"/>
+      <c r="AA107" s="10" t="n"/>
+      <c r="AB107" s="10" t="n"/>
+      <c r="AC107" s="10" t="n"/>
+      <c r="AD107" s="10" t="n"/>
+      <c r="AE107" s="10" t="n"/>
+      <c r="AF107" s="10" t="n"/>
+      <c r="AG107" s="10" t="n"/>
+      <c r="AH107" s="10" t="n"/>
+      <c r="AI107" s="10" t="n"/>
+      <c r="AJ107" s="10" t="n"/>
+      <c r="AK107" s="11" t="n"/>
+    </row>
+    <row r="108" ht="36" customHeight="1">
+      <c r="C108" s="41" t="inlineStr">
         <is>
           <t>新規履歴 INSERT（対象購読者ごと、`zenkai_hanbaiten_id` = 更新前の販売店ID）：</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="409" customHeight="1">
-      <c r="C108" s="42" t="inlineStr">
+    <row r="109" ht="409" customHeight="1">
+      <c r="C109" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_dokusya_rireki (
   dokusya_id, rireki_no, ja_id, kanri_shiten_id, shiten_id, kumiaiin_code,
@@ -10660,7 +10799,7 @@
   shoki_dokusya_kaishi_date, dokusya_kaishi_date, dokusya_chushi_date, joho_henko_tekiyo_date,
   seikyu_kaishi_month, biko, henko_riyu,
   saishin_data_flg, zougen_hokoku_flg, shinki_flg, kaiyaku_flg,
-  zenkai_hanbaiten_id, hanbaiten_tekiyo_date,
+  zenkai_hanbaiten_id,
   created_at, created_by
 )
 SELECT
@@ -10676,82 +10815,75 @@
   d.hanbaiten_id, d.tanka_id, d.yubin_kubun, d.shiharai_hoho, d.dokusyaryo_shiharai_cycle,
   d.bank_branch_code, d.bank_branch_name, d.hikiotoshi_yokin_shubetsu, d.hikiotoshi_koza_no, d.hikiotoshi_koza_meigi,
   d.dokusyaso_bunrui, d.nogyosya_bunrui,
-  d.shoki_dokusya_kaishi_date, d.dokusya_kaishi_date, d.dokusya_chushi_date, :hanbaiten_tekiyo_date,
+  d.shoki_dokusya_kaishi_date, d.dokusya_kaishi_date, d.dokusya_chushi_date, :joho_henko_tekiyo_date,
   d.seikyu_kaishi_month, d.biko, '販売店一括置換',
   TRUE, TRUE, FALSE, FALSE,
-  :zenkai_hanbaiten_id_per_dokusya, :hanbaiten_tekiyo_date,
+  :zenkai_hanbaiten_id_per_dokusya,
   NOW(), :user_account_id
 FROM t_dokusya d
 WHERE d.dokusya_id = :dokusya_id</t>
         </is>
       </c>
-      <c r="D108" s="10" t="n"/>
-      <c r="E108" s="10" t="n"/>
-      <c r="F108" s="10" t="n"/>
-      <c r="G108" s="10" t="n"/>
-      <c r="H108" s="10" t="n"/>
-      <c r="I108" s="10" t="n"/>
-      <c r="J108" s="10" t="n"/>
-      <c r="K108" s="10" t="n"/>
-      <c r="L108" s="10" t="n"/>
-      <c r="M108" s="10" t="n"/>
-      <c r="N108" s="10" t="n"/>
-      <c r="O108" s="10" t="n"/>
-      <c r="P108" s="10" t="n"/>
-      <c r="Q108" s="10" t="n"/>
-      <c r="R108" s="10" t="n"/>
-      <c r="S108" s="10" t="n"/>
-      <c r="T108" s="10" t="n"/>
-      <c r="U108" s="10" t="n"/>
-      <c r="V108" s="10" t="n"/>
-      <c r="W108" s="10" t="n"/>
-      <c r="X108" s="10" t="n"/>
-      <c r="Y108" s="10" t="n"/>
-      <c r="Z108" s="10" t="n"/>
-      <c r="AA108" s="10" t="n"/>
-      <c r="AB108" s="10" t="n"/>
-      <c r="AC108" s="10" t="n"/>
-      <c r="AD108" s="10" t="n"/>
-      <c r="AE108" s="10" t="n"/>
-      <c r="AF108" s="10" t="n"/>
-      <c r="AG108" s="10" t="n"/>
-      <c r="AH108" s="10" t="n"/>
-      <c r="AI108" s="10" t="n"/>
-      <c r="AJ108" s="10" t="n"/>
-      <c r="AK108" s="11" t="n"/>
-    </row>
-    <row r="109" ht="18" customHeight="1">
-      <c r="C109" s="41" t="inlineStr">
-        <is>
-          <t>`henko_riyu`：`'販売店一括置換'` を設定する。</t>
-        </is>
-      </c>
+      <c r="D109" s="10" t="n"/>
+      <c r="E109" s="10" t="n"/>
+      <c r="F109" s="10" t="n"/>
+      <c r="G109" s="10" t="n"/>
+      <c r="H109" s="10" t="n"/>
+      <c r="I109" s="10" t="n"/>
+      <c r="J109" s="10" t="n"/>
+      <c r="K109" s="10" t="n"/>
+      <c r="L109" s="10" t="n"/>
+      <c r="M109" s="10" t="n"/>
+      <c r="N109" s="10" t="n"/>
+      <c r="O109" s="10" t="n"/>
+      <c r="P109" s="10" t="n"/>
+      <c r="Q109" s="10" t="n"/>
+      <c r="R109" s="10" t="n"/>
+      <c r="S109" s="10" t="n"/>
+      <c r="T109" s="10" t="n"/>
+      <c r="U109" s="10" t="n"/>
+      <c r="V109" s="10" t="n"/>
+      <c r="W109" s="10" t="n"/>
+      <c r="X109" s="10" t="n"/>
+      <c r="Y109" s="10" t="n"/>
+      <c r="Z109" s="10" t="n"/>
+      <c r="AA109" s="10" t="n"/>
+      <c r="AB109" s="10" t="n"/>
+      <c r="AC109" s="10" t="n"/>
+      <c r="AD109" s="10" t="n"/>
+      <c r="AE109" s="10" t="n"/>
+      <c r="AF109" s="10" t="n"/>
+      <c r="AG109" s="10" t="n"/>
+      <c r="AH109" s="10" t="n"/>
+      <c r="AI109" s="10" t="n"/>
+      <c r="AJ109" s="10" t="n"/>
+      <c r="AK109" s="11" t="n"/>
     </row>
     <row r="110" ht="18" customHeight="1">
       <c r="C110" s="41" t="inlineStr">
         <is>
+          <t>`henko_riyu`：`'販売店一括置換'` を設定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="C111" s="41" t="inlineStr">
+        <is>
           <t>`zougen_hokoku_flg`：販売店変更のため `TRUE`（増減報告対象）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="36" customHeight="1">
-      <c r="C111" s="41" t="inlineStr">
-        <is>
-          <t>`zenkai_hanbaiten_id`：更新前の `t_dokusya.hanbaiten_id`（4.3 で取得した値）を設定する。</t>
         </is>
       </c>
     </row>
     <row r="112" ht="36" customHeight="1">
       <c r="C112" s="41" t="inlineStr">
         <is>
-          <t>`hanbaiten_tekiyo_date`：リクエストの `hanbaiten_tekiyo_date` を設定する。</t>
+          <t>`zenkai_hanbaiten_id`：更新前の `t_dokusya.hanbaiten_id`（4.3 で取得した値）を設定する。</t>
         </is>
       </c>
     </row>
     <row r="113" ht="90" customHeight="1">
       <c r="C113" s="41" t="inlineStr">
         <is>
-          <t>`joho_henko_tekiyo_date`（顧客要件 2026-06）：**販売店のみ変更イベントのため `hanbaiten_tekiyo_date` と同じ適用日を設定する**（`hanbaiten_tekiyo_date = joho_henko_tekiyo_date`。UI 編集 Rule2 / SCR-011 §8.1・§14.3 と同一）。マスタ側 `t_dokusya.joho_henko_tekiyo_date` も同日に更新し、最新履歴（saishin）と整合させる。</t>
+          <t>`joho_henko_tekiyo_date`：リクエストの `joho_henko_tekiyo_date` を設定する（販売店のみ変更イベント。専用の適用日列は廃止し適用日を joho に一本化・顧客要件 2026-07。UI 編集 Rule2 / SCR-011 §8.1・§14.3 と同一）。マスタ側 `t_dokusya.joho_henko_tekiyo_date` も同日に更新し、最新履歴（saishin）と整合させる。</t>
         </is>
       </c>
     </row>
@@ -10827,7 +10959,7 @@
     <row r="118" ht="54" customHeight="1">
       <c r="C118" s="41" t="inlineStr">
         <is>
-          <t>`after_value`：置換結果サマリ JSON `{ "total_count", "new_hanbaiten_id", "hanbaiten_tekiyo_date", "rireki_count" }`</t>
+          <t>`after_value`：置換結果サマリ JSON `{ "total_count", "new_hanbaiten_id", "joho_henko_tekiyo_date", "rireki_count" }`</t>
         </is>
       </c>
     </row>
@@ -10845,7 +10977,7 @@
   "total_count": 3,
   "replaced_count": 3,
   "new_hanbaiten_id": 201,
-  "hanbaiten_tekiyo_date": "2026-06-01",
+  "joho_henko_tekiyo_date": "2026-06-01",
   "rireki_count": 3,
   "dokusya_ids": [5001, 5002, 5003]
 }</t>
@@ -10992,7 +11124,6 @@
     </row>
   </sheetData>
   <mergeCells count="213">
-    <mergeCell ref="B102:AK102"/>
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Y28:AB28"/>
     <mergeCell ref="C57:AK57"/>
@@ -11005,6 +11136,7 @@
     <mergeCell ref="D78:AK78"/>
     <mergeCell ref="T33:X33"/>
     <mergeCell ref="AC23:AE23"/>
+    <mergeCell ref="C102:AK102"/>
     <mergeCell ref="M32:P32"/>
     <mergeCell ref="N18:AK18"/>
     <mergeCell ref="C86:AK86"/>
@@ -11037,7 +11169,6 @@
     <mergeCell ref="C127:AK127"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="M35:P35"/>
-    <mergeCell ref="C80:AK80"/>
     <mergeCell ref="AF36:AK36"/>
     <mergeCell ref="C129:AK129"/>
     <mergeCell ref="Q25:S25"/>
@@ -11057,6 +11188,7 @@
     <mergeCell ref="M25:P25"/>
     <mergeCell ref="T28:X28"/>
     <mergeCell ref="C48:AK48"/>
+    <mergeCell ref="B91:AK91"/>
     <mergeCell ref="T37:X37"/>
     <mergeCell ref="C106:AK106"/>
     <mergeCell ref="Y25:AB25"/>
@@ -11077,8 +11209,10 @@
     <mergeCell ref="C42:AK42"/>
     <mergeCell ref="D37:L37"/>
     <mergeCell ref="C88:AK88"/>
+    <mergeCell ref="D98:AK98"/>
     <mergeCell ref="C126:AK126"/>
     <mergeCell ref="AF32:AK32"/>
+    <mergeCell ref="B103:AK103"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF26:AK26"/>
     <mergeCell ref="C24:L24"/>
@@ -11087,10 +11221,8 @@
     <mergeCell ref="AD2:AG3"/>
     <mergeCell ref="C33:L33"/>
     <mergeCell ref="B13:I13"/>
-    <mergeCell ref="C103:AK103"/>
     <mergeCell ref="AF38:AK38"/>
     <mergeCell ref="C117:AK117"/>
-    <mergeCell ref="C99:AK99"/>
     <mergeCell ref="Q32:S32"/>
     <mergeCell ref="D38:L38"/>
     <mergeCell ref="C26:L26"/>
@@ -11110,7 +11242,6 @@
     <mergeCell ref="D76:AK76"/>
     <mergeCell ref="C122:AK122"/>
     <mergeCell ref="B41:I41"/>
-    <mergeCell ref="B90:AK90"/>
     <mergeCell ref="B50:I50"/>
     <mergeCell ref="M27:P27"/>
     <mergeCell ref="M36:P36"/>
@@ -11121,11 +11252,13 @@
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="J7:AK7"/>
     <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="C96:AK96"/>
     <mergeCell ref="T32:X32"/>
     <mergeCell ref="C87:AK87"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="Q34:S34"/>
     <mergeCell ref="C28:L28"/>
+    <mergeCell ref="C82:AK82"/>
     <mergeCell ref="AC25:AE25"/>
     <mergeCell ref="A72:AK72"/>
     <mergeCell ref="C107:AK107"/>
@@ -11148,10 +11281,10 @@
     <mergeCell ref="Y35:AE35"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
+    <mergeCell ref="D80:AK80"/>
     <mergeCell ref="C105:AK105"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="AH1:AK1"/>
-    <mergeCell ref="D96:AK96"/>
     <mergeCell ref="C120:AK120"/>
     <mergeCell ref="C119:AK119"/>
     <mergeCell ref="V2:Y3"/>
@@ -11173,26 +11306,26 @@
     <mergeCell ref="M24:P24"/>
     <mergeCell ref="C69:AK69"/>
     <mergeCell ref="M38:P38"/>
-    <mergeCell ref="C83:AK83"/>
     <mergeCell ref="AC26:AE26"/>
     <mergeCell ref="T35:X35"/>
     <mergeCell ref="C92:AK92"/>
-    <mergeCell ref="B98:AK98"/>
     <mergeCell ref="Y23:AB23"/>
     <mergeCell ref="Y32:AE32"/>
     <mergeCell ref="T25:X25"/>
-    <mergeCell ref="B82:AK82"/>
     <mergeCell ref="Y38:AE38"/>
     <mergeCell ref="J14:M14"/>
+    <mergeCell ref="B99:AK99"/>
     <mergeCell ref="B44:I44"/>
     <mergeCell ref="A30:AK30"/>
     <mergeCell ref="AC27:AE27"/>
     <mergeCell ref="B53:I53"/>
     <mergeCell ref="B74:AK74"/>
+    <mergeCell ref="B83:AK83"/>
     <mergeCell ref="C124:AK124"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="C90:AK90"/>
     <mergeCell ref="AF39:AK39"/>
     <mergeCell ref="C60:AK60"/>
     <mergeCell ref="Q28:S28"/>
@@ -11202,7 +11335,6 @@
     <mergeCell ref="C110:AK110"/>
     <mergeCell ref="Y34:AE34"/>
     <mergeCell ref="Q39:S39"/>
-    <mergeCell ref="C91:AK91"/>
     <mergeCell ref="M28:P28"/>
     <mergeCell ref="M37:P37"/>
   </mergeCells>
@@ -11377,7 +11509,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/18</t>
+          <t>2026/07/23</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -13797,7 +13929,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/18</t>
+          <t>2026/07/23</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>

--- a/docs/design/ACSMS-SCR-015/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者販売店一括置換画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-015/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者販売店一括置換画面_V1.0.xlsx
@@ -1354,7 +1354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG7"/>
+  <dimension ref="A1:AG10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -1809,21 +1809,204 @@
       <c r="AF7" s="10" t="n"/>
       <c r="AG7" s="11" t="n"/>
     </row>
+    <row r="8" ht="19.5" customHeight="1">
+      <c r="A8" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11" t="n"/>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>2026/07/24</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="11" t="n"/>
+      <c r="H8" s="17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I8" s="10" t="n"/>
+      <c r="J8" s="11" t="n"/>
+      <c r="K8" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="n"/>
+      <c r="M8" s="10" t="n"/>
+      <c r="N8" s="10" t="n"/>
+      <c r="O8" s="10" t="n"/>
+      <c r="P8" s="10" t="n"/>
+      <c r="Q8" s="11" t="n"/>
+      <c r="R8" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件（2026-07）：検索 API の `hanbaiten_id`（**置換元配達販売店**）を**必須**化。置換対象の判定を現行 master の販売店から **as-of 適用日** に変更：各購読者の「適用日時点で有効な履歴レコード」（`t_dokusya_rireki` で `joho_henko_tekiyo_date ≦ 適用日` の最大 joho・`DISTINCT ON(dokusya_id)`）の配達販売店 = 置換元、かつ適用日時点で購読中（購読中/種別/`kaishi ≦ 適用日 &lt; chushi`）の購読者のみ返す。未来の適用日でもその時点の販売店で母集合を確定する。§4.3 §4.4 §4.5・リクエストパラメータ No.7 を更新。</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="n"/>
+      <c r="T8" s="10" t="n"/>
+      <c r="U8" s="10" t="n"/>
+      <c r="V8" s="11" t="n"/>
+      <c r="W8" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X8" s="10" t="n"/>
+      <c r="Y8" s="10" t="n"/>
+      <c r="Z8" s="10" t="n"/>
+      <c r="AA8" s="11" t="n"/>
+      <c r="AB8" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC8" s="10" t="n"/>
+      <c r="AD8" s="10" t="n"/>
+      <c r="AE8" s="10" t="n"/>
+      <c r="AF8" s="10" t="n"/>
+      <c r="AG8" s="11" t="n"/>
+    </row>
+    <row r="9" ht="19.5" customHeight="1">
+      <c r="A9" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>2026/07/24</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="11" t="n"/>
+      <c r="H9" s="17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I9" s="10" t="n"/>
+      <c r="J9" s="11" t="n"/>
+      <c r="K9" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="n"/>
+      <c r="M9" s="10" t="n"/>
+      <c r="N9" s="10" t="n"/>
+      <c r="O9" s="10" t="n"/>
+      <c r="P9" s="10" t="n"/>
+      <c r="Q9" s="11" t="n"/>
+      <c r="R9" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件（2026-07）：検索 API に `new_hanbaiten_id`（**置換先配達販売店**）を**必須**追加。検索は「= 置換元 かつ ≠ 置換先」で絞り込み（as-of 有効レコードの配達販売店に `eff.hanbaiten_id &lt;&gt; :new_hanbaiten_id` を追加）、既に置換先を配達している購読者を除外する（置換元 = 置換先 は 0 件・FE で事前弾き）。FE は置換先を検索エリア（適用日の直後）へ移動し、選択後の置換先入力欄を廃止して検索条件の値を置換実行にそのまま用いる。リクエストパラメータ No.7.5・§概要・§4.3 を更新。</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="n"/>
+      <c r="T9" s="10" t="n"/>
+      <c r="U9" s="10" t="n"/>
+      <c r="V9" s="11" t="n"/>
+      <c r="W9" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X9" s="10" t="n"/>
+      <c r="Y9" s="10" t="n"/>
+      <c r="Z9" s="10" t="n"/>
+      <c r="AA9" s="11" t="n"/>
+      <c r="AB9" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC9" s="10" t="n"/>
+      <c r="AD9" s="10" t="n"/>
+      <c r="AE9" s="10" t="n"/>
+      <c r="AF9" s="10" t="n"/>
+      <c r="AG9" s="11" t="n"/>
+    </row>
+    <row r="10" ht="19.5" customHeight="1">
+      <c r="A10" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="11" t="n"/>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>2026/07/25</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="11" t="n"/>
+      <c r="H10" s="17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I10" s="10" t="n"/>
+      <c r="J10" s="11" t="n"/>
+      <c r="K10" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L10" s="10" t="n"/>
+      <c r="M10" s="10" t="n"/>
+      <c r="N10" s="10" t="n"/>
+      <c r="O10" s="10" t="n"/>
+      <c r="P10" s="10" t="n"/>
+      <c r="Q10" s="11" t="n"/>
+      <c r="R10" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件（2026-07 改訂）：`hanbaiten_id`（配達販売店）を**必須→任意**へ戻す（ラベルも「置換元配達販売店」→「配達販売店」）。指定時のみ `eff.hanbaiten_id = :hanbaiten_id` で追加絞り込み、未指定なら「置換先以外の全販売店」が対象。`new_hanbaiten_id`（置換先）は引き続き必須で `≠ 置換先` を常に適用。§概要・リクエストパラメータ No.7・§4.3 を更新。</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="n"/>
+      <c r="T10" s="10" t="n"/>
+      <c r="U10" s="10" t="n"/>
+      <c r="V10" s="11" t="n"/>
+      <c r="W10" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X10" s="10" t="n"/>
+      <c r="Y10" s="10" t="n"/>
+      <c r="Z10" s="10" t="n"/>
+      <c r="AA10" s="11" t="n"/>
+      <c r="AB10" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC10" s="10" t="n"/>
+      <c r="AD10" s="10" t="n"/>
+      <c r="AE10" s="10" t="n"/>
+      <c r="AF10" s="10" t="n"/>
+      <c r="AG10" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="49">
+  <mergeCells count="70">
     <mergeCell ref="R1:V1"/>
+    <mergeCell ref="R8:V8"/>
     <mergeCell ref="AB1:AG1"/>
     <mergeCell ref="C6:G6"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="W10:AA10"/>
     <mergeCell ref="R5:V5"/>
     <mergeCell ref="W6:AA6"/>
+    <mergeCell ref="AB9:AG9"/>
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="K7:Q7"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="W5:AA5"/>
     <mergeCell ref="R4:V4"/>
+    <mergeCell ref="R10:V10"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="H7:J7"/>
+    <mergeCell ref="K10:Q10"/>
     <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="R7:V7"/>
@@ -1831,33 +2014,48 @@
     <mergeCell ref="K6:Q6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="R6:V6"/>
+    <mergeCell ref="C10:G10"/>
     <mergeCell ref="C1:G1"/>
     <mergeCell ref="K3:Q3"/>
     <mergeCell ref="W4:AA4"/>
     <mergeCell ref="W1:AA1"/>
     <mergeCell ref="W3:AA3"/>
     <mergeCell ref="H3:J3"/>
+    <mergeCell ref="AB8:AG8"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="K9:Q9"/>
     <mergeCell ref="AB7:AG7"/>
     <mergeCell ref="K5:Q5"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="AB10:AG10"/>
     <mergeCell ref="W7:AA7"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H5:J5"/>
     <mergeCell ref="A5:B5"/>
+    <mergeCell ref="H8:J8"/>
     <mergeCell ref="R3:V3"/>
     <mergeCell ref="AB3:AG3"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:G8"/>
     <mergeCell ref="K1:Q1"/>
     <mergeCell ref="AB6:AG6"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="W9:AA9"/>
     <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="W8:AA8"/>
     <mergeCell ref="AB5:AG5"/>
     <mergeCell ref="W2:AA2"/>
+    <mergeCell ref="A10:B10"/>
     <mergeCell ref="H4:J4"/>
     <mergeCell ref="R2:V2"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="K8:Q8"/>
     <mergeCell ref="AB4:AG4"/>
     <mergeCell ref="K2:Q2"/>
+    <mergeCell ref="R9:V9"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H6:J6"/>
   </mergeCells>
@@ -2032,7 +2230,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/23</t>
+          <t>2026/07/25</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2548,7 +2746,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/23</t>
+          <t>2026/07/25</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3477,7 +3675,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/23</t>
+          <t>2026/07/25</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3622,7 +3820,7 @@
       <c r="R6" s="11" t="n"/>
       <c r="S6" s="19" t="inlineStr">
         <is>
-          <t>販売店一括置換対象の購読者を検索する（検索条件 + DataScope + ページネーション対応）。`tetsuzuki_shurui=1`（購読中）のみ返却。`joho_henko_tekiyo_date`（適用日）は**必須**で、その適用日時点で置換可能な購読者のみ返却する（顧客要件 2026-07：画面初期表示では検索しない・適用日を入力して検索する運用）。</t>
+          <t>販売店一括置換対象の購読者を検索する（検索条件 + DataScope + ページネーション対応）。`joho_henko_tekiyo_date`（適用日）・`new_hanbaiten_id`（**置換先**）は**必須**、`hanbaiten_id`（配達販売店）は**任意**。適用日時点で有効な履歴レコード（as-of 適用日）の配達販売店が **置換先と一致せず**（配達販売店を指定した場合はさらに **その値と一致**）、その時点で購読中の購読者のみ返却する（顧客要件 2026-07：画面初期表示では検索しない・適用日＋置換先を入力して検索する運用）。</t>
         </is>
       </c>
       <c r="T6" s="10" t="n"/>
@@ -3877,7 +4075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK145"/>
+  <dimension ref="A1:AK149"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -4038,7 +4236,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/23</t>
+          <t>2026/07/25</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -4147,7 +4345,7 @@
       <c r="AJ7" s="10" t="n"/>
       <c r="AK7" s="11" t="n"/>
     </row>
-    <row r="8" ht="36" customHeight="1">
+    <row r="8" ht="54" customHeight="1">
       <c r="B8" s="33" t="inlineStr">
         <is>
           <t>概要</t>
@@ -4162,7 +4360,7 @@
       <c r="I8" s="11" t="n"/>
       <c r="J8" s="19" t="inlineStr">
         <is>
-          <t>販売店一括置換対象の購読者を検索する（検索条件 + DataScope + ページネーション対応）。`tetsuzuki_shurui=1`（購読中）のみ返却。`joho_henko_tekiyo_date`（適用日）は**必須**で、その適用日時点で置換可能な購読者のみ返却する（顧客要件 2026-07：画面初期表示では検索しない・適用日を入力して検索する運用）。</t>
+          <t>販売店一括置換対象の購読者を検索する（検索条件 + DataScope + ページネーション対応）。`joho_henko_tekiyo_date`（適用日）・`new_hanbaiten_id`（**置換先**）は**必須**、`hanbaiten_id`（配達販売店）は**任意**。適用日時点で有効な履歴レコード（as-of 適用日）の配達販売店が **置換先と一致せず**（配達販売店を指定した場合はさらに **その値と一致**）、その時点で購読中の購読者のみ返却する（顧客要件 2026-07：画面初期表示では検索しない・適用日＋置換先を入力して検索する運用）。</t>
         </is>
       </c>
       <c r="K8" s="10" t="n"/>
@@ -5084,7 +5282,7 @@
       <c r="AJ28" s="10" t="n"/>
       <c r="AK28" s="11" t="n"/>
     </row>
-    <row r="29" ht="18" customHeight="1">
+    <row r="29" ht="72" customHeight="1">
       <c r="B29" s="31" t="n">
         <v>7</v>
       </c>
@@ -5139,7 +5337,7 @@
       <c r="AE29" s="11" t="n"/>
       <c r="AF29" s="19" t="inlineStr">
         <is>
-          <t>配達販売店ID（完全一致）</t>
+          <t>配達販売店ID（**任意**）。指定時のみ、適用日時点で有効な履歴（`joho_henko_tekiyo_date ≦ 適用日` の最大 joho）の配達販売店がこの値の購読者に追加で絞り込む（後述 §置換可能条件・as-of 適用日）。未指定なら置換先以外の全販売店が対象</t>
         </is>
       </c>
       <c r="AG29" s="10" t="n"/>
@@ -5148,13 +5346,13 @@
       <c r="AJ29" s="10" t="n"/>
       <c r="AK29" s="11" t="n"/>
     </row>
-    <row r="30" ht="36" customHeight="1">
+    <row r="30" ht="72" customHeight="1">
       <c r="B30" s="31" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="C30" s="19" t="inlineStr">
         <is>
-          <t>dokusya_kaishi_date_from</t>
+          <t>new_hanbaiten_id</t>
         </is>
       </c>
       <c r="D30" s="10" t="n"/>
@@ -5168,7 +5366,7 @@
       <c r="L30" s="11" t="n"/>
       <c r="M30" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N30" s="10" t="n"/>
@@ -5179,7 +5377,7 @@
       <c r="S30" s="11" t="n"/>
       <c r="T30" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="U30" s="10" t="n"/>
@@ -5194,14 +5392,16 @@
       <c r="Z30" s="10" t="n"/>
       <c r="AA30" s="10" t="n"/>
       <c r="AB30" s="11" t="n"/>
-      <c r="AC30" s="17" t="n">
-        <v>10</v>
+      <c r="AC30" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AD30" s="10" t="n"/>
       <c r="AE30" s="11" t="n"/>
       <c r="AF30" s="19" t="inlineStr">
         <is>
-          <t>購読開始日（開始）YYYY-MM-DD。`shoki_dokusya_kaishi_date &gt;= :date_from` で範囲検索</t>
+          <t>置換先配達販売店ID（**必須**）。検索では有効履歴の配達販売店がこの値**でない**購読者に絞る（= 置換元 かつ ≠ 置換先）。置換元と同一だと 0 件（FE で事前バリデーション）。置換実行 API の `new_hanbaiten_id` と同一値。未選択は HTTP 400（`置換先配達販売店を選択してください。`）</t>
         </is>
       </c>
       <c r="AG30" s="10" t="n"/>
@@ -5212,11 +5412,11 @@
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="B31" s="31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
-          <t>dokusya_kaishi_date_to</t>
+          <t>dokusya_kaishi_date_from</t>
         </is>
       </c>
       <c r="D31" s="10" t="n"/>
@@ -5263,7 +5463,7 @@
       <c r="AE31" s="11" t="n"/>
       <c r="AF31" s="19" t="inlineStr">
         <is>
-          <t>購読開始日（終了）YYYY-MM-DD。`shoki_dokusya_kaishi_date &lt;= :date_to` で範囲検索</t>
+          <t>購読開始日（開始）YYYY-MM-DD。`shoki_dokusya_kaishi_date &gt;= :date_from` で範囲検索</t>
         </is>
       </c>
       <c r="AG31" s="10" t="n"/>
@@ -5272,13 +5472,13 @@
       <c r="AJ31" s="10" t="n"/>
       <c r="AK31" s="11" t="n"/>
     </row>
-    <row r="32" ht="54" customHeight="1">
+    <row r="32" ht="36" customHeight="1">
       <c r="B32" s="31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>joho_henko_tekiyo_date</t>
+          <t>dokusya_kaishi_date_to</t>
         </is>
       </c>
       <c r="D32" s="10" t="n"/>
@@ -5303,7 +5503,7 @@
       <c r="S32" s="11" t="n"/>
       <c r="T32" s="17" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U32" s="10" t="n"/>
@@ -5325,7 +5525,7 @@
       <c r="AE32" s="11" t="n"/>
       <c r="AF32" s="19" t="inlineStr">
         <is>
-          <t>適用日 YYYY-MM-DD。**必須**。**紙版=未来日のみ（`&gt; 当日`）**（顧客要件 2026-07 改訂）。この適用日時点で置換可能な購読者のみ返却する（後述 §置換可能条件）。置換実行 API の適用日と同一基準</t>
+          <t>購読開始日（終了）YYYY-MM-DD。`shoki_dokusya_kaishi_date &lt;= :date_to` で範囲検索</t>
         </is>
       </c>
       <c r="AG32" s="10" t="n"/>
@@ -5334,13 +5534,13 @@
       <c r="AJ32" s="10" t="n"/>
       <c r="AK32" s="11" t="n"/>
     </row>
-    <row r="33" ht="90" customHeight="1">
+    <row r="33" ht="54" customHeight="1">
       <c r="B33" s="31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C33" s="19" t="inlineStr">
         <is>
-          <t>dokusya_shubetsu</t>
+          <t>joho_henko_tekiyo_date</t>
         </is>
       </c>
       <c r="D33" s="10" t="n"/>
@@ -5354,7 +5554,7 @@
       <c r="L33" s="11" t="n"/>
       <c r="M33" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N33" s="10" t="n"/>
@@ -5380,16 +5580,14 @@
       <c r="Z33" s="10" t="n"/>
       <c r="AA33" s="10" t="n"/>
       <c r="AB33" s="11" t="n"/>
-      <c r="AC33" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AC33" s="17" t="n">
+        <v>10</v>
       </c>
       <c r="AD33" s="10" t="n"/>
       <c r="AE33" s="11" t="n"/>
       <c r="AF33" s="19" t="inlineStr">
         <is>
-          <t>購読種別（**必須・1:紙版 / 2:電子版**。3:併読 は対象外）。この種別で購読者を絞り込む（`d.dokusya_shubetsu = :dokusya_shubetsu`）。**電子版(2) は本画面の対象外** → 日付に関係なく `VALIDATION_ERROR`（`電子版は本画面では対象外です。`／ACSMS-MSG-015-009・顧客要件 2026-07 改訂）</t>
+          <t>適用日 YYYY-MM-DD。**必須**。**紙版=未来日のみ（`&gt; 当日`）**（顧客要件 2026-07 改訂）。この適用日時点で置換可能な購読者のみ返却する（後述 §置換可能条件）。置換実行 API の適用日と同一基準</t>
         </is>
       </c>
       <c r="AG33" s="10" t="n"/>
@@ -5398,13 +5596,13 @@
       <c r="AJ33" s="10" t="n"/>
       <c r="AK33" s="11" t="n"/>
     </row>
-    <row r="34" ht="18" customHeight="1">
+    <row r="34" ht="90" customHeight="1">
       <c r="B34" s="31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C34" s="19" t="inlineStr">
         <is>
-          <t>page</t>
+          <t>dokusya_shubetsu</t>
         </is>
       </c>
       <c r="D34" s="10" t="n"/>
@@ -5429,7 +5627,7 @@
       <c r="S34" s="11" t="n"/>
       <c r="T34" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="U34" s="10" t="n"/>
@@ -5453,7 +5651,7 @@
       <c r="AE34" s="11" t="n"/>
       <c r="AF34" s="19" t="inlineStr">
         <is>
-          <t>ページ番号（デフォルト: 1）</t>
+          <t>購読種別（**必須・1:紙版 / 2:電子版**。3:併読 は対象外）。この種別で購読者を絞り込む（`d.dokusya_shubetsu = :dokusya_shubetsu`）。**電子版(2) は本画面の対象外** → 日付に関係なく `VALIDATION_ERROR`（`電子版は本画面では対象外です。`／ACSMS-MSG-015-009・顧客要件 2026-07 改訂）</t>
         </is>
       </c>
       <c r="AG34" s="10" t="n"/>
@@ -5468,7 +5666,7 @@
       </c>
       <c r="C35" s="19" t="inlineStr">
         <is>
-          <t>per_page</t>
+          <t>page</t>
         </is>
       </c>
       <c r="D35" s="10" t="n"/>
@@ -5517,7 +5715,7 @@
       <c r="AE35" s="11" t="n"/>
       <c r="AF35" s="19" t="inlineStr">
         <is>
-          <t>1ページの件数（デフォルト: 20、最大: 100）</t>
+          <t>ページ番号（デフォルト: 1）</t>
         </is>
       </c>
       <c r="AG35" s="10" t="n"/>
@@ -5526,13 +5724,13 @@
       <c r="AJ35" s="10" t="n"/>
       <c r="AK35" s="11" t="n"/>
     </row>
-    <row r="36" ht="54" customHeight="1">
+    <row r="36" ht="18" customHeight="1">
       <c r="B36" s="31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C36" s="19" t="inlineStr">
         <is>
-          <t>sort_by</t>
+          <t>per_page</t>
         </is>
       </c>
       <c r="D36" s="10" t="n"/>
@@ -5546,7 +5744,7 @@
       <c r="L36" s="11" t="n"/>
       <c r="M36" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N36" s="10" t="n"/>
@@ -5581,7 +5779,7 @@
       <c r="AE36" s="11" t="n"/>
       <c r="AF36" s="19" t="inlineStr">
         <is>
-          <t>ソートカラム（許可: `kanri_shiten_name` / `shiten_name` / `kumiaiin_code` / `hanbaiten_code`。デフォルト: `kumiaiin_code`）</t>
+          <t>1ページの件数（デフォルト: 20、最大: 100）</t>
         </is>
       </c>
       <c r="AG36" s="10" t="n"/>
@@ -5590,13 +5788,13 @@
       <c r="AJ36" s="10" t="n"/>
       <c r="AK36" s="11" t="n"/>
     </row>
-    <row r="37" ht="18" customHeight="1">
+    <row r="37" ht="54" customHeight="1">
       <c r="B37" s="31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C37" s="19" t="inlineStr">
         <is>
-          <t>sort_order</t>
+          <t>sort_by</t>
         </is>
       </c>
       <c r="D37" s="10" t="n"/>
@@ -5645,7 +5843,7 @@
       <c r="AE37" s="11" t="n"/>
       <c r="AF37" s="19" t="inlineStr">
         <is>
-          <t>ソート順（asc / desc、デフォルト: asc）</t>
+          <t>ソートカラム（許可: `kanri_shiten_name` / `shiten_name` / `kumiaiin_code` / `hanbaiten_code`。デフォルト: `kumiaiin_code`）</t>
         </is>
       </c>
       <c r="AG37" s="10" t="n"/>
@@ -5654,88 +5852,88 @@
       <c r="AJ37" s="10" t="n"/>
       <c r="AK37" s="11" t="n"/>
     </row>
-    <row r="38" ht="19.5" customHeight="1"/>
-    <row r="39" ht="19.5" customHeight="1">
-      <c r="A39" s="27" t="inlineStr">
+    <row r="38" ht="18" customHeight="1">
+      <c r="B38" s="31" t="n">
+        <v>14</v>
+      </c>
+      <c r="C38" s="19" t="inlineStr">
+        <is>
+          <t>sort_order</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
+      <c r="G38" s="10" t="n"/>
+      <c r="H38" s="10" t="n"/>
+      <c r="I38" s="10" t="n"/>
+      <c r="J38" s="10" t="n"/>
+      <c r="K38" s="10" t="n"/>
+      <c r="L38" s="11" t="n"/>
+      <c r="M38" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N38" s="10" t="n"/>
+      <c r="O38" s="10" t="n"/>
+      <c r="P38" s="11" t="n"/>
+      <c r="Q38" s="17" t="inlineStr"/>
+      <c r="R38" s="10" t="n"/>
+      <c r="S38" s="11" t="n"/>
+      <c r="T38" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U38" s="10" t="n"/>
+      <c r="V38" s="10" t="n"/>
+      <c r="W38" s="10" t="n"/>
+      <c r="X38" s="11" t="n"/>
+      <c r="Y38" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z38" s="10" t="n"/>
+      <c r="AA38" s="10" t="n"/>
+      <c r="AB38" s="11" t="n"/>
+      <c r="AC38" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD38" s="10" t="n"/>
+      <c r="AE38" s="11" t="n"/>
+      <c r="AF38" s="19" t="inlineStr">
+        <is>
+          <t>ソート順（asc / desc、デフォルト: asc）</t>
+        </is>
+      </c>
+      <c r="AG38" s="10" t="n"/>
+      <c r="AH38" s="10" t="n"/>
+      <c r="AI38" s="10" t="n"/>
+      <c r="AJ38" s="10" t="n"/>
+      <c r="AK38" s="11" t="n"/>
+    </row>
+    <row r="39" ht="19.5" customHeight="1"/>
+    <row r="40" ht="19.5" customHeight="1">
+      <c r="A40" s="27" t="inlineStr">
         <is>
           <t>3.レスポンスデータ</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="19.5" customHeight="1"/>
-    <row r="41" ht="19.5" customHeight="1">
-      <c r="B41" s="30" t="inlineStr">
+    <row r="41" ht="19.5" customHeight="1"/>
+    <row r="42" ht="19.5" customHeight="1">
+      <c r="B42" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C41" s="16" t="inlineStr">
+      <c r="C42" s="16" t="inlineStr">
         <is>
           <t>項目ID</t>
-        </is>
-      </c>
-      <c r="D41" s="10" t="n"/>
-      <c r="E41" s="10" t="n"/>
-      <c r="F41" s="10" t="n"/>
-      <c r="G41" s="10" t="n"/>
-      <c r="H41" s="10" t="n"/>
-      <c r="I41" s="10" t="n"/>
-      <c r="J41" s="10" t="n"/>
-      <c r="K41" s="10" t="n"/>
-      <c r="L41" s="11" t="n"/>
-      <c r="M41" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
-        </is>
-      </c>
-      <c r="N41" s="10" t="n"/>
-      <c r="O41" s="10" t="n"/>
-      <c r="P41" s="11" t="n"/>
-      <c r="Q41" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
-        </is>
-      </c>
-      <c r="R41" s="10" t="n"/>
-      <c r="S41" s="11" t="n"/>
-      <c r="T41" s="16" t="inlineStr">
-        <is>
-          <t>フォーマット</t>
-        </is>
-      </c>
-      <c r="U41" s="10" t="n"/>
-      <c r="V41" s="10" t="n"/>
-      <c r="W41" s="10" t="n"/>
-      <c r="X41" s="11" t="n"/>
-      <c r="Y41" s="16" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
-      <c r="Z41" s="10" t="n"/>
-      <c r="AA41" s="10" t="n"/>
-      <c r="AB41" s="10" t="n"/>
-      <c r="AC41" s="10" t="n"/>
-      <c r="AD41" s="10" t="n"/>
-      <c r="AE41" s="11" t="n"/>
-      <c r="AF41" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="AG41" s="10" t="n"/>
-      <c r="AH41" s="10" t="n"/>
-      <c r="AI41" s="10" t="n"/>
-      <c r="AJ41" s="10" t="n"/>
-      <c r="AK41" s="11" t="n"/>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="B42" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C42" s="19" t="inlineStr">
-        <is>
-          <t>data</t>
         </is>
       </c>
       <c r="D42" s="10" t="n"/>
@@ -5747,25 +5945,33 @@
       <c r="J42" s="10" t="n"/>
       <c r="K42" s="10" t="n"/>
       <c r="L42" s="11" t="n"/>
-      <c r="M42" s="17" t="inlineStr">
-        <is>
-          <t>Array</t>
+      <c r="M42" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
         </is>
       </c>
       <c r="N42" s="10" t="n"/>
       <c r="O42" s="10" t="n"/>
       <c r="P42" s="11" t="n"/>
-      <c r="Q42" s="17" t="inlineStr"/>
+      <c r="Q42" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
+        </is>
+      </c>
       <c r="R42" s="10" t="n"/>
       <c r="S42" s="11" t="n"/>
-      <c r="T42" s="17" t="inlineStr"/>
+      <c r="T42" s="16" t="inlineStr">
+        <is>
+          <t>フォーマット</t>
+        </is>
+      </c>
       <c r="U42" s="10" t="n"/>
       <c r="V42" s="10" t="n"/>
       <c r="W42" s="10" t="n"/>
       <c r="X42" s="11" t="n"/>
-      <c r="Y42" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Y42" s="16" t="inlineStr">
+        <is>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="Z42" s="10" t="n"/>
@@ -5774,9 +5980,9 @@
       <c r="AC42" s="10" t="n"/>
       <c r="AD42" s="10" t="n"/>
       <c r="AE42" s="11" t="n"/>
-      <c r="AF42" s="19" t="inlineStr">
-        <is>
-          <t>購読者一覧</t>
+      <c r="AF42" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="AG42" s="10" t="n"/>
@@ -5787,14 +5993,14 @@
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C43" s="37" t="n"/>
-      <c r="D43" s="19" t="inlineStr">
-        <is>
-          <t>dokusya_id</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C43" s="19" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="n"/>
       <c r="E43" s="10" t="n"/>
       <c r="F43" s="10" t="n"/>
       <c r="G43" s="10" t="n"/>
@@ -5805,7 +6011,7 @@
       <c r="L43" s="11" t="n"/>
       <c r="M43" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="N43" s="10" t="n"/>
@@ -5832,7 +6038,7 @@
       <c r="AE43" s="11" t="n"/>
       <c r="AF43" s="19" t="inlineStr">
         <is>
-          <t>購読者ID</t>
+          <t>購読者一覧</t>
         </is>
       </c>
       <c r="AG43" s="10" t="n"/>
@@ -5843,12 +6049,12 @@
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="C44" s="38" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="C44" s="37" t="n"/>
       <c r="D44" s="19" t="inlineStr">
         <is>
-          <t>kanri_shiten_id</t>
+          <t>dokusya_id</t>
         </is>
       </c>
       <c r="E44" s="10" t="n"/>
@@ -5877,7 +6083,7 @@
       <c r="X44" s="11" t="n"/>
       <c r="Y44" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z44" s="10" t="n"/>
@@ -5888,7 +6094,7 @@
       <c r="AE44" s="11" t="n"/>
       <c r="AF44" s="19" t="inlineStr">
         <is>
-          <t>管理支店ID</t>
+          <t>購読者ID</t>
         </is>
       </c>
       <c r="AG44" s="10" t="n"/>
@@ -5897,14 +6103,14 @@
       <c r="AJ44" s="10" t="n"/>
       <c r="AK44" s="11" t="n"/>
     </row>
-    <row r="45" ht="36" customHeight="1">
+    <row r="45" ht="18" customHeight="1">
       <c r="B45" s="31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C45" s="38" t="n"/>
       <c r="D45" s="19" t="inlineStr">
         <is>
-          <t>kanri_shiten_name</t>
+          <t>kanri_shiten_id</t>
         </is>
       </c>
       <c r="E45" s="10" t="n"/>
@@ -5917,7 +6123,7 @@
       <c r="L45" s="11" t="n"/>
       <c r="M45" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N45" s="10" t="n"/>
@@ -5944,7 +6150,7 @@
       <c r="AE45" s="11" t="n"/>
       <c r="AF45" s="19" t="inlineStr">
         <is>
-          <t>管理支店名（`m_kanri_shiten.kanri_shiten_name` を LEFT JOIN）</t>
+          <t>管理支店ID</t>
         </is>
       </c>
       <c r="AG45" s="10" t="n"/>
@@ -5953,14 +6159,14 @@
       <c r="AJ45" s="10" t="n"/>
       <c r="AK45" s="11" t="n"/>
     </row>
-    <row r="46" ht="18" customHeight="1">
+    <row r="46" ht="36" customHeight="1">
       <c r="B46" s="31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C46" s="38" t="n"/>
       <c r="D46" s="19" t="inlineStr">
         <is>
-          <t>shiten_id</t>
+          <t>kanri_shiten_name</t>
         </is>
       </c>
       <c r="E46" s="10" t="n"/>
@@ -5973,7 +6179,7 @@
       <c r="L46" s="11" t="n"/>
       <c r="M46" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N46" s="10" t="n"/>
@@ -6000,7 +6206,7 @@
       <c r="AE46" s="11" t="n"/>
       <c r="AF46" s="19" t="inlineStr">
         <is>
-          <t>支店ID</t>
+          <t>管理支店名（`m_kanri_shiten.kanri_shiten_name` を LEFT JOIN）</t>
         </is>
       </c>
       <c r="AG46" s="10" t="n"/>
@@ -6009,14 +6215,14 @@
       <c r="AJ46" s="10" t="n"/>
       <c r="AK46" s="11" t="n"/>
     </row>
-    <row r="47" ht="36" customHeight="1">
+    <row r="47" ht="18" customHeight="1">
       <c r="B47" s="31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C47" s="38" t="n"/>
       <c r="D47" s="19" t="inlineStr">
         <is>
-          <t>shiten_name</t>
+          <t>shiten_id</t>
         </is>
       </c>
       <c r="E47" s="10" t="n"/>
@@ -6029,7 +6235,7 @@
       <c r="L47" s="11" t="n"/>
       <c r="M47" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N47" s="10" t="n"/>
@@ -6056,7 +6262,7 @@
       <c r="AE47" s="11" t="n"/>
       <c r="AF47" s="19" t="inlineStr">
         <is>
-          <t>支店名（`m_shiten.shiten_name` を LEFT JOIN）</t>
+          <t>支店ID</t>
         </is>
       </c>
       <c r="AG47" s="10" t="n"/>
@@ -6065,14 +6271,14 @@
       <c r="AJ47" s="10" t="n"/>
       <c r="AK47" s="11" t="n"/>
     </row>
-    <row r="48" ht="18" customHeight="1">
+    <row r="48" ht="36" customHeight="1">
       <c r="B48" s="31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C48" s="38" t="n"/>
       <c r="D48" s="19" t="inlineStr">
         <is>
-          <t>kumiaiin_code</t>
+          <t>shiten_name</t>
         </is>
       </c>
       <c r="E48" s="10" t="n"/>
@@ -6101,7 +6307,7 @@
       <c r="X48" s="11" t="n"/>
       <c r="Y48" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z48" s="10" t="n"/>
@@ -6112,7 +6318,7 @@
       <c r="AE48" s="11" t="n"/>
       <c r="AF48" s="19" t="inlineStr">
         <is>
-          <t>組合員コード（空文字許容）</t>
+          <t>支店名（`m_shiten.shiten_name` を LEFT JOIN）</t>
         </is>
       </c>
       <c r="AG48" s="10" t="n"/>
@@ -6121,14 +6327,14 @@
       <c r="AJ48" s="10" t="n"/>
       <c r="AK48" s="11" t="n"/>
     </row>
-    <row r="49" ht="36" customHeight="1">
+    <row r="49" ht="18" customHeight="1">
       <c r="B49" s="31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C49" s="38" t="n"/>
       <c r="D49" s="19" t="inlineStr">
         <is>
-          <t>shimei</t>
+          <t>kumiaiin_code</t>
         </is>
       </c>
       <c r="E49" s="10" t="n"/>
@@ -6168,7 +6374,7 @@
       <c r="AE49" s="11" t="n"/>
       <c r="AF49" s="19" t="inlineStr">
         <is>
-          <t>氏名（`shimei_sei + ' ' + shimei_mei` を結合）</t>
+          <t>組合員コード（空文字許容）</t>
         </is>
       </c>
       <c r="AG49" s="10" t="n"/>
@@ -6177,14 +6383,14 @@
       <c r="AJ49" s="10" t="n"/>
       <c r="AK49" s="11" t="n"/>
     </row>
-    <row r="50" ht="18" customHeight="1">
+    <row r="50" ht="36" customHeight="1">
       <c r="B50" s="31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C50" s="38" t="n"/>
       <c r="D50" s="19" t="inlineStr">
         <is>
-          <t>haitatsu_yubin_no</t>
+          <t>shimei</t>
         </is>
       </c>
       <c r="E50" s="10" t="n"/>
@@ -6224,7 +6430,7 @@
       <c r="AE50" s="11" t="n"/>
       <c r="AF50" s="19" t="inlineStr">
         <is>
-          <t>配達先郵便番号（空文字許容）</t>
+          <t>氏名（`shimei_sei + ' ' + shimei_mei` を結合）</t>
         </is>
       </c>
       <c r="AG50" s="10" t="n"/>
@@ -6233,14 +6439,14 @@
       <c r="AJ50" s="10" t="n"/>
       <c r="AK50" s="11" t="n"/>
     </row>
-    <row r="51" ht="72" customHeight="1">
+    <row r="51" ht="18" customHeight="1">
       <c r="B51" s="31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C51" s="38" t="n"/>
       <c r="D51" s="19" t="inlineStr">
         <is>
-          <t>haitatsu_address</t>
+          <t>haitatsu_yubin_no</t>
         </is>
       </c>
       <c r="E51" s="10" t="n"/>
@@ -6280,7 +6486,7 @@
       <c r="AE51" s="11" t="n"/>
       <c r="AF51" s="19" t="inlineStr">
         <is>
-          <t>配達先住所（`m_todofuken.todofuken_name + haitatsu_shikuchoson + haitatsu_chome_banchi + haitatsu_tatemono_mei` を結合）</t>
+          <t>配達先郵便番号（空文字許容）</t>
         </is>
       </c>
       <c r="AG51" s="10" t="n"/>
@@ -6289,14 +6495,14 @@
       <c r="AJ51" s="10" t="n"/>
       <c r="AK51" s="11" t="n"/>
     </row>
-    <row r="52" ht="18" customHeight="1">
+    <row r="52" ht="72" customHeight="1">
       <c r="B52" s="31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C52" s="38" t="n"/>
       <c r="D52" s="19" t="inlineStr">
         <is>
-          <t>hanbaiten_id</t>
+          <t>haitatsu_address</t>
         </is>
       </c>
       <c r="E52" s="10" t="n"/>
@@ -6309,7 +6515,7 @@
       <c r="L52" s="11" t="n"/>
       <c r="M52" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N52" s="10" t="n"/>
@@ -6336,7 +6542,7 @@
       <c r="AE52" s="11" t="n"/>
       <c r="AF52" s="19" t="inlineStr">
         <is>
-          <t>販売店ID</t>
+          <t>配達先住所（`m_todofuken.todofuken_name + haitatsu_shikuchoson + haitatsu_chome_banchi + haitatsu_tatemono_mei` を結合）</t>
         </is>
       </c>
       <c r="AG52" s="10" t="n"/>
@@ -6345,14 +6551,14 @@
       <c r="AJ52" s="10" t="n"/>
       <c r="AK52" s="11" t="n"/>
     </row>
-    <row r="53" ht="36" customHeight="1">
+    <row r="53" ht="18" customHeight="1">
       <c r="B53" s="31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C53" s="38" t="n"/>
       <c r="D53" s="19" t="inlineStr">
         <is>
-          <t>hanbaiten_code</t>
+          <t>hanbaiten_id</t>
         </is>
       </c>
       <c r="E53" s="10" t="n"/>
@@ -6365,7 +6571,7 @@
       <c r="L53" s="11" t="n"/>
       <c r="M53" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N53" s="10" t="n"/>
@@ -6392,7 +6598,7 @@
       <c r="AE53" s="11" t="n"/>
       <c r="AF53" s="19" t="inlineStr">
         <is>
-          <t>販売店コード（`m_hanbaiten.hanbaiten_code` を JOIN）</t>
+          <t>販売店ID</t>
         </is>
       </c>
       <c r="AG53" s="10" t="n"/>
@@ -6403,12 +6609,12 @@
     </row>
     <row r="54" ht="36" customHeight="1">
       <c r="B54" s="31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C54" s="38" t="n"/>
       <c r="D54" s="19" t="inlineStr">
         <is>
-          <t>hanbaiten_name</t>
+          <t>hanbaiten_code</t>
         </is>
       </c>
       <c r="E54" s="10" t="n"/>
@@ -6448,7 +6654,7 @@
       <c r="AE54" s="11" t="n"/>
       <c r="AF54" s="19" t="inlineStr">
         <is>
-          <t>販売店名（`m_hanbaiten.hanbaiten_name` を JOIN）</t>
+          <t>販売店コード（`m_hanbaiten.hanbaiten_code` を JOIN）</t>
         </is>
       </c>
       <c r="AG54" s="10" t="n"/>
@@ -6457,14 +6663,14 @@
       <c r="AJ54" s="10" t="n"/>
       <c r="AK54" s="11" t="n"/>
     </row>
-    <row r="55" ht="54" customHeight="1">
+    <row r="55" ht="36" customHeight="1">
       <c r="B55" s="31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C55" s="38" t="n"/>
       <c r="D55" s="19" t="inlineStr">
         <is>
-          <t>dokusya_shubetsu</t>
+          <t>hanbaiten_name</t>
         </is>
       </c>
       <c r="E55" s="10" t="n"/>
@@ -6477,7 +6683,7 @@
       <c r="L55" s="11" t="n"/>
       <c r="M55" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N55" s="10" t="n"/>
@@ -6504,7 +6710,7 @@
       <c r="AE55" s="11" t="n"/>
       <c r="AF55" s="19" t="inlineStr">
         <is>
-          <t>購読種別 ※m_code.code_category='DOKUSYA_SHUBETSU'を参照（1:紙版, 2:電子版, 3:併読）</t>
+          <t>販売店名（`m_hanbaiten.hanbaiten_name` を JOIN）</t>
         </is>
       </c>
       <c r="AG55" s="10" t="n"/>
@@ -6513,14 +6719,14 @@
       <c r="AJ55" s="10" t="n"/>
       <c r="AK55" s="11" t="n"/>
     </row>
-    <row r="56" ht="36" customHeight="1">
+    <row r="56" ht="54" customHeight="1">
       <c r="B56" s="31" t="n">
-        <v>15</v>
-      </c>
-      <c r="C56" s="39" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="C56" s="38" t="n"/>
       <c r="D56" s="19" t="inlineStr">
         <is>
-          <t>shiharai_hoho</t>
+          <t>dokusya_shubetsu</t>
         </is>
       </c>
       <c r="E56" s="10" t="n"/>
@@ -6560,7 +6766,7 @@
       <c r="AE56" s="11" t="n"/>
       <c r="AF56" s="19" t="inlineStr">
         <is>
-          <t>支払方法 ※m_code.code_category='SHIHARAI_HOHO'を参照（1〜9）</t>
+          <t>購読種別 ※m_code.code_category='DOKUSYA_SHUBETSU'を参照（1:紙版, 2:電子版, 3:併読）</t>
         </is>
       </c>
       <c r="AG56" s="10" t="n"/>
@@ -6569,16 +6775,16 @@
       <c r="AJ56" s="10" t="n"/>
       <c r="AK56" s="11" t="n"/>
     </row>
-    <row r="57" ht="18" customHeight="1">
+    <row r="57" ht="36" customHeight="1">
       <c r="B57" s="31" t="n">
-        <v>16</v>
-      </c>
-      <c r="C57" s="19" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
-      <c r="D57" s="10" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="C57" s="39" t="n"/>
+      <c r="D57" s="19" t="inlineStr">
+        <is>
+          <t>shiharai_hoho</t>
+        </is>
+      </c>
       <c r="E57" s="10" t="n"/>
       <c r="F57" s="10" t="n"/>
       <c r="G57" s="10" t="n"/>
@@ -6589,7 +6795,7 @@
       <c r="L57" s="11" t="n"/>
       <c r="M57" s="17" t="inlineStr">
         <is>
-          <t>Object</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N57" s="10" t="n"/>
@@ -6616,7 +6822,7 @@
       <c r="AE57" s="11" t="n"/>
       <c r="AF57" s="19" t="inlineStr">
         <is>
-          <t>ページネーション情報</t>
+          <t>支払方法 ※m_code.code_category='SHIHARAI_HOHO'を参照（1〜9）</t>
         </is>
       </c>
       <c r="AG57" s="10" t="n"/>
@@ -6627,14 +6833,14 @@
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="B58" s="31" t="n">
-        <v>17</v>
-      </c>
-      <c r="C58" s="37" t="n"/>
-      <c r="D58" s="19" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C58" s="19" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="n"/>
       <c r="E58" s="10" t="n"/>
       <c r="F58" s="10" t="n"/>
       <c r="G58" s="10" t="n"/>
@@ -6645,7 +6851,7 @@
       <c r="L58" s="11" t="n"/>
       <c r="M58" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="N58" s="10" t="n"/>
@@ -6672,7 +6878,7 @@
       <c r="AE58" s="11" t="n"/>
       <c r="AF58" s="19" t="inlineStr">
         <is>
-          <t>総件数</t>
+          <t>ページネーション情報</t>
         </is>
       </c>
       <c r="AG58" s="10" t="n"/>
@@ -6683,12 +6889,12 @@
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="B59" s="31" t="n">
-        <v>18</v>
-      </c>
-      <c r="C59" s="38" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="C59" s="37" t="n"/>
       <c r="D59" s="19" t="inlineStr">
         <is>
-          <t>page</t>
+          <t>total</t>
         </is>
       </c>
       <c r="E59" s="10" t="n"/>
@@ -6728,7 +6934,7 @@
       <c r="AE59" s="11" t="n"/>
       <c r="AF59" s="19" t="inlineStr">
         <is>
-          <t>現在ページ番号</t>
+          <t>総件数</t>
         </is>
       </c>
       <c r="AG59" s="10" t="n"/>
@@ -6739,12 +6945,12 @@
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="B60" s="31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C60" s="38" t="n"/>
       <c r="D60" s="19" t="inlineStr">
         <is>
-          <t>per_page</t>
+          <t>page</t>
         </is>
       </c>
       <c r="E60" s="10" t="n"/>
@@ -6784,7 +6990,7 @@
       <c r="AE60" s="11" t="n"/>
       <c r="AF60" s="19" t="inlineStr">
         <is>
-          <t>1ページの件数</t>
+          <t>現在ページ番号</t>
         </is>
       </c>
       <c r="AG60" s="10" t="n"/>
@@ -6795,12 +7001,12 @@
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="B61" s="31" t="n">
-        <v>20</v>
-      </c>
-      <c r="C61" s="39" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="C61" s="38" t="n"/>
       <c r="D61" s="19" t="inlineStr">
         <is>
-          <t>total_pages</t>
+          <t>per_page</t>
         </is>
       </c>
       <c r="E61" s="10" t="n"/>
@@ -6840,7 +7046,7 @@
       <c r="AE61" s="11" t="n"/>
       <c r="AF61" s="19" t="inlineStr">
         <is>
-          <t>総ページ数</t>
+          <t>1ページの件数</t>
         </is>
       </c>
       <c r="AG61" s="10" t="n"/>
@@ -6849,64 +7055,120 @@
       <c r="AJ61" s="10" t="n"/>
       <c r="AK61" s="11" t="n"/>
     </row>
-    <row r="62" ht="19.5" customHeight="1"/>
-    <row r="63" ht="19.5" customHeight="1">
-      <c r="B63" s="40" t="inlineStr">
+    <row r="62" ht="18" customHeight="1">
+      <c r="B62" s="31" t="n">
+        <v>20</v>
+      </c>
+      <c r="C62" s="39" t="n"/>
+      <c r="D62" s="19" t="inlineStr">
+        <is>
+          <t>total_pages</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="n"/>
+      <c r="F62" s="10" t="n"/>
+      <c r="G62" s="10" t="n"/>
+      <c r="H62" s="10" t="n"/>
+      <c r="I62" s="10" t="n"/>
+      <c r="J62" s="10" t="n"/>
+      <c r="K62" s="10" t="n"/>
+      <c r="L62" s="11" t="n"/>
+      <c r="M62" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N62" s="10" t="n"/>
+      <c r="O62" s="10" t="n"/>
+      <c r="P62" s="11" t="n"/>
+      <c r="Q62" s="17" t="inlineStr"/>
+      <c r="R62" s="10" t="n"/>
+      <c r="S62" s="11" t="n"/>
+      <c r="T62" s="17" t="inlineStr"/>
+      <c r="U62" s="10" t="n"/>
+      <c r="V62" s="10" t="n"/>
+      <c r="W62" s="10" t="n"/>
+      <c r="X62" s="11" t="n"/>
+      <c r="Y62" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z62" s="10" t="n"/>
+      <c r="AA62" s="10" t="n"/>
+      <c r="AB62" s="10" t="n"/>
+      <c r="AC62" s="10" t="n"/>
+      <c r="AD62" s="10" t="n"/>
+      <c r="AE62" s="11" t="n"/>
+      <c r="AF62" s="19" t="inlineStr">
+        <is>
+          <t>総ページ数</t>
+        </is>
+      </c>
+      <c r="AG62" s="10" t="n"/>
+      <c r="AH62" s="10" t="n"/>
+      <c r="AI62" s="10" t="n"/>
+      <c r="AJ62" s="10" t="n"/>
+      <c r="AK62" s="11" t="n"/>
+    </row>
+    <row r="63" ht="19.5" customHeight="1"/>
+    <row r="64" ht="19.5" customHeight="1">
+      <c r="B64" s="40" t="inlineStr">
         <is>
           <t>リクエスト</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="C64" s="19" t="inlineStr">
+    <row r="65" ht="18" customHeight="1">
+      <c r="C65" s="19" t="inlineStr">
         <is>
           <t>GET /api/v1/dokusya/replace-hanbaiten/search?joho_henko_tekiyo_date=2026-08-01&amp;kanri_shiten_id=10&amp;kumiaiin_code=10001&amp;page=1&amp;per_page=20&amp;sort_by=kumiaiin_code&amp;sort_order=asc</t>
         </is>
       </c>
-      <c r="D64" s="10" t="n"/>
-      <c r="E64" s="10" t="n"/>
-      <c r="F64" s="10" t="n"/>
-      <c r="G64" s="10" t="n"/>
-      <c r="H64" s="10" t="n"/>
-      <c r="I64" s="10" t="n"/>
-      <c r="J64" s="10" t="n"/>
-      <c r="K64" s="10" t="n"/>
-      <c r="L64" s="10" t="n"/>
-      <c r="M64" s="10" t="n"/>
-      <c r="N64" s="10" t="n"/>
-      <c r="O64" s="10" t="n"/>
-      <c r="P64" s="10" t="n"/>
-      <c r="Q64" s="10" t="n"/>
-      <c r="R64" s="10" t="n"/>
-      <c r="S64" s="10" t="n"/>
-      <c r="T64" s="10" t="n"/>
-      <c r="U64" s="10" t="n"/>
-      <c r="V64" s="10" t="n"/>
-      <c r="W64" s="10" t="n"/>
-      <c r="X64" s="10" t="n"/>
-      <c r="Y64" s="10" t="n"/>
-      <c r="Z64" s="10" t="n"/>
-      <c r="AA64" s="10" t="n"/>
-      <c r="AB64" s="10" t="n"/>
-      <c r="AC64" s="10" t="n"/>
-      <c r="AD64" s="10" t="n"/>
-      <c r="AE64" s="10" t="n"/>
-      <c r="AF64" s="10" t="n"/>
-      <c r="AG64" s="10" t="n"/>
-      <c r="AH64" s="10" t="n"/>
-      <c r="AI64" s="10" t="n"/>
-      <c r="AJ64" s="10" t="n"/>
-      <c r="AK64" s="11" t="n"/>
-    </row>
-    <row r="66" ht="19.5" customHeight="1">
-      <c r="B66" s="40" t="inlineStr">
+      <c r="D65" s="10" t="n"/>
+      <c r="E65" s="10" t="n"/>
+      <c r="F65" s="10" t="n"/>
+      <c r="G65" s="10" t="n"/>
+      <c r="H65" s="10" t="n"/>
+      <c r="I65" s="10" t="n"/>
+      <c r="J65" s="10" t="n"/>
+      <c r="K65" s="10" t="n"/>
+      <c r="L65" s="10" t="n"/>
+      <c r="M65" s="10" t="n"/>
+      <c r="N65" s="10" t="n"/>
+      <c r="O65" s="10" t="n"/>
+      <c r="P65" s="10" t="n"/>
+      <c r="Q65" s="10" t="n"/>
+      <c r="R65" s="10" t="n"/>
+      <c r="S65" s="10" t="n"/>
+      <c r="T65" s="10" t="n"/>
+      <c r="U65" s="10" t="n"/>
+      <c r="V65" s="10" t="n"/>
+      <c r="W65" s="10" t="n"/>
+      <c r="X65" s="10" t="n"/>
+      <c r="Y65" s="10" t="n"/>
+      <c r="Z65" s="10" t="n"/>
+      <c r="AA65" s="10" t="n"/>
+      <c r="AB65" s="10" t="n"/>
+      <c r="AC65" s="10" t="n"/>
+      <c r="AD65" s="10" t="n"/>
+      <c r="AE65" s="10" t="n"/>
+      <c r="AF65" s="10" t="n"/>
+      <c r="AG65" s="10" t="n"/>
+      <c r="AH65" s="10" t="n"/>
+      <c r="AI65" s="10" t="n"/>
+      <c r="AJ65" s="10" t="n"/>
+      <c r="AK65" s="11" t="n"/>
+    </row>
+    <row r="67" ht="19.5" customHeight="1">
+      <c r="B67" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="409" customHeight="1">
-      <c r="C67" s="19" t="inlineStr">
+    <row r="68" ht="409" customHeight="1">
+      <c r="C68" s="19" t="inlineStr">
         <is>
           <t>{
   "data": [
@@ -6952,50 +7214,50 @@
 }</t>
         </is>
       </c>
-      <c r="D67" s="10" t="n"/>
-      <c r="E67" s="10" t="n"/>
-      <c r="F67" s="10" t="n"/>
-      <c r="G67" s="10" t="n"/>
-      <c r="H67" s="10" t="n"/>
-      <c r="I67" s="10" t="n"/>
-      <c r="J67" s="10" t="n"/>
-      <c r="K67" s="10" t="n"/>
-      <c r="L67" s="10" t="n"/>
-      <c r="M67" s="10" t="n"/>
-      <c r="N67" s="10" t="n"/>
-      <c r="O67" s="10" t="n"/>
-      <c r="P67" s="10" t="n"/>
-      <c r="Q67" s="10" t="n"/>
-      <c r="R67" s="10" t="n"/>
-      <c r="S67" s="10" t="n"/>
-      <c r="T67" s="10" t="n"/>
-      <c r="U67" s="10" t="n"/>
-      <c r="V67" s="10" t="n"/>
-      <c r="W67" s="10" t="n"/>
-      <c r="X67" s="10" t="n"/>
-      <c r="Y67" s="10" t="n"/>
-      <c r="Z67" s="10" t="n"/>
-      <c r="AA67" s="10" t="n"/>
-      <c r="AB67" s="10" t="n"/>
-      <c r="AC67" s="10" t="n"/>
-      <c r="AD67" s="10" t="n"/>
-      <c r="AE67" s="10" t="n"/>
-      <c r="AF67" s="10" t="n"/>
-      <c r="AG67" s="10" t="n"/>
-      <c r="AH67" s="10" t="n"/>
-      <c r="AI67" s="10" t="n"/>
-      <c r="AJ67" s="10" t="n"/>
-      <c r="AK67" s="11" t="n"/>
-    </row>
-    <row r="69" ht="19.5" customHeight="1">
-      <c r="B69" s="40" t="inlineStr">
+      <c r="D68" s="10" t="n"/>
+      <c r="E68" s="10" t="n"/>
+      <c r="F68" s="10" t="n"/>
+      <c r="G68" s="10" t="n"/>
+      <c r="H68" s="10" t="n"/>
+      <c r="I68" s="10" t="n"/>
+      <c r="J68" s="10" t="n"/>
+      <c r="K68" s="10" t="n"/>
+      <c r="L68" s="10" t="n"/>
+      <c r="M68" s="10" t="n"/>
+      <c r="N68" s="10" t="n"/>
+      <c r="O68" s="10" t="n"/>
+      <c r="P68" s="10" t="n"/>
+      <c r="Q68" s="10" t="n"/>
+      <c r="R68" s="10" t="n"/>
+      <c r="S68" s="10" t="n"/>
+      <c r="T68" s="10" t="n"/>
+      <c r="U68" s="10" t="n"/>
+      <c r="V68" s="10" t="n"/>
+      <c r="W68" s="10" t="n"/>
+      <c r="X68" s="10" t="n"/>
+      <c r="Y68" s="10" t="n"/>
+      <c r="Z68" s="10" t="n"/>
+      <c r="AA68" s="10" t="n"/>
+      <c r="AB68" s="10" t="n"/>
+      <c r="AC68" s="10" t="n"/>
+      <c r="AD68" s="10" t="n"/>
+      <c r="AE68" s="10" t="n"/>
+      <c r="AF68" s="10" t="n"/>
+      <c r="AG68" s="10" t="n"/>
+      <c r="AH68" s="10" t="n"/>
+      <c r="AI68" s="10" t="n"/>
+      <c r="AJ68" s="10" t="n"/>
+      <c r="AK68" s="11" t="n"/>
+    </row>
+    <row r="70" ht="19.5" customHeight="1">
+      <c r="B70" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Bad Request (Date Range Invalid)）</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="72" customHeight="1">
-      <c r="C70" s="19" t="inlineStr">
+    <row r="71" ht="72" customHeight="1">
+      <c r="C71" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "DATE_RANGE_INVALID",
@@ -7003,50 +7265,50 @@
 }</t>
         </is>
       </c>
-      <c r="D70" s="10" t="n"/>
-      <c r="E70" s="10" t="n"/>
-      <c r="F70" s="10" t="n"/>
-      <c r="G70" s="10" t="n"/>
-      <c r="H70" s="10" t="n"/>
-      <c r="I70" s="10" t="n"/>
-      <c r="J70" s="10" t="n"/>
-      <c r="K70" s="10" t="n"/>
-      <c r="L70" s="10" t="n"/>
-      <c r="M70" s="10" t="n"/>
-      <c r="N70" s="10" t="n"/>
-      <c r="O70" s="10" t="n"/>
-      <c r="P70" s="10" t="n"/>
-      <c r="Q70" s="10" t="n"/>
-      <c r="R70" s="10" t="n"/>
-      <c r="S70" s="10" t="n"/>
-      <c r="T70" s="10" t="n"/>
-      <c r="U70" s="10" t="n"/>
-      <c r="V70" s="10" t="n"/>
-      <c r="W70" s="10" t="n"/>
-      <c r="X70" s="10" t="n"/>
-      <c r="Y70" s="10" t="n"/>
-      <c r="Z70" s="10" t="n"/>
-      <c r="AA70" s="10" t="n"/>
-      <c r="AB70" s="10" t="n"/>
-      <c r="AC70" s="10" t="n"/>
-      <c r="AD70" s="10" t="n"/>
-      <c r="AE70" s="10" t="n"/>
-      <c r="AF70" s="10" t="n"/>
-      <c r="AG70" s="10" t="n"/>
-      <c r="AH70" s="10" t="n"/>
-      <c r="AI70" s="10" t="n"/>
-      <c r="AJ70" s="10" t="n"/>
-      <c r="AK70" s="11" t="n"/>
-    </row>
-    <row r="72" ht="19.5" customHeight="1">
-      <c r="B72" s="40" t="inlineStr">
+      <c r="D71" s="10" t="n"/>
+      <c r="E71" s="10" t="n"/>
+      <c r="F71" s="10" t="n"/>
+      <c r="G71" s="10" t="n"/>
+      <c r="H71" s="10" t="n"/>
+      <c r="I71" s="10" t="n"/>
+      <c r="J71" s="10" t="n"/>
+      <c r="K71" s="10" t="n"/>
+      <c r="L71" s="10" t="n"/>
+      <c r="M71" s="10" t="n"/>
+      <c r="N71" s="10" t="n"/>
+      <c r="O71" s="10" t="n"/>
+      <c r="P71" s="10" t="n"/>
+      <c r="Q71" s="10" t="n"/>
+      <c r="R71" s="10" t="n"/>
+      <c r="S71" s="10" t="n"/>
+      <c r="T71" s="10" t="n"/>
+      <c r="U71" s="10" t="n"/>
+      <c r="V71" s="10" t="n"/>
+      <c r="W71" s="10" t="n"/>
+      <c r="X71" s="10" t="n"/>
+      <c r="Y71" s="10" t="n"/>
+      <c r="Z71" s="10" t="n"/>
+      <c r="AA71" s="10" t="n"/>
+      <c r="AB71" s="10" t="n"/>
+      <c r="AC71" s="10" t="n"/>
+      <c r="AD71" s="10" t="n"/>
+      <c r="AE71" s="10" t="n"/>
+      <c r="AF71" s="10" t="n"/>
+      <c r="AG71" s="10" t="n"/>
+      <c r="AH71" s="10" t="n"/>
+      <c r="AI71" s="10" t="n"/>
+      <c r="AJ71" s="10" t="n"/>
+      <c r="AK71" s="11" t="n"/>
+    </row>
+    <row r="73" ht="19.5" customHeight="1">
+      <c r="B73" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Bad Request (Validation Error)）</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="126" customHeight="1">
-      <c r="C73" s="19" t="inlineStr">
+    <row r="74" ht="126" customHeight="1">
+      <c r="C74" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "VALIDATION_ERROR",
@@ -7057,50 +7319,50 @@
 }</t>
         </is>
       </c>
-      <c r="D73" s="10" t="n"/>
-      <c r="E73" s="10" t="n"/>
-      <c r="F73" s="10" t="n"/>
-      <c r="G73" s="10" t="n"/>
-      <c r="H73" s="10" t="n"/>
-      <c r="I73" s="10" t="n"/>
-      <c r="J73" s="10" t="n"/>
-      <c r="K73" s="10" t="n"/>
-      <c r="L73" s="10" t="n"/>
-      <c r="M73" s="10" t="n"/>
-      <c r="N73" s="10" t="n"/>
-      <c r="O73" s="10" t="n"/>
-      <c r="P73" s="10" t="n"/>
-      <c r="Q73" s="10" t="n"/>
-      <c r="R73" s="10" t="n"/>
-      <c r="S73" s="10" t="n"/>
-      <c r="T73" s="10" t="n"/>
-      <c r="U73" s="10" t="n"/>
-      <c r="V73" s="10" t="n"/>
-      <c r="W73" s="10" t="n"/>
-      <c r="X73" s="10" t="n"/>
-      <c r="Y73" s="10" t="n"/>
-      <c r="Z73" s="10" t="n"/>
-      <c r="AA73" s="10" t="n"/>
-      <c r="AB73" s="10" t="n"/>
-      <c r="AC73" s="10" t="n"/>
-      <c r="AD73" s="10" t="n"/>
-      <c r="AE73" s="10" t="n"/>
-      <c r="AF73" s="10" t="n"/>
-      <c r="AG73" s="10" t="n"/>
-      <c r="AH73" s="10" t="n"/>
-      <c r="AI73" s="10" t="n"/>
-      <c r="AJ73" s="10" t="n"/>
-      <c r="AK73" s="11" t="n"/>
-    </row>
-    <row r="75" ht="19.5" customHeight="1">
-      <c r="B75" s="40" t="inlineStr">
+      <c r="D74" s="10" t="n"/>
+      <c r="E74" s="10" t="n"/>
+      <c r="F74" s="10" t="n"/>
+      <c r="G74" s="10" t="n"/>
+      <c r="H74" s="10" t="n"/>
+      <c r="I74" s="10" t="n"/>
+      <c r="J74" s="10" t="n"/>
+      <c r="K74" s="10" t="n"/>
+      <c r="L74" s="10" t="n"/>
+      <c r="M74" s="10" t="n"/>
+      <c r="N74" s="10" t="n"/>
+      <c r="O74" s="10" t="n"/>
+      <c r="P74" s="10" t="n"/>
+      <c r="Q74" s="10" t="n"/>
+      <c r="R74" s="10" t="n"/>
+      <c r="S74" s="10" t="n"/>
+      <c r="T74" s="10" t="n"/>
+      <c r="U74" s="10" t="n"/>
+      <c r="V74" s="10" t="n"/>
+      <c r="W74" s="10" t="n"/>
+      <c r="X74" s="10" t="n"/>
+      <c r="Y74" s="10" t="n"/>
+      <c r="Z74" s="10" t="n"/>
+      <c r="AA74" s="10" t="n"/>
+      <c r="AB74" s="10" t="n"/>
+      <c r="AC74" s="10" t="n"/>
+      <c r="AD74" s="10" t="n"/>
+      <c r="AE74" s="10" t="n"/>
+      <c r="AF74" s="10" t="n"/>
+      <c r="AG74" s="10" t="n"/>
+      <c r="AH74" s="10" t="n"/>
+      <c r="AI74" s="10" t="n"/>
+      <c r="AJ74" s="10" t="n"/>
+      <c r="AK74" s="11" t="n"/>
+    </row>
+    <row r="76" ht="19.5" customHeight="1">
+      <c r="B76" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="72" customHeight="1">
-      <c r="C76" s="19" t="inlineStr">
+    <row r="77" ht="72" customHeight="1">
+      <c r="C77" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -7108,50 +7370,50 @@
 }</t>
         </is>
       </c>
-      <c r="D76" s="10" t="n"/>
-      <c r="E76" s="10" t="n"/>
-      <c r="F76" s="10" t="n"/>
-      <c r="G76" s="10" t="n"/>
-      <c r="H76" s="10" t="n"/>
-      <c r="I76" s="10" t="n"/>
-      <c r="J76" s="10" t="n"/>
-      <c r="K76" s="10" t="n"/>
-      <c r="L76" s="10" t="n"/>
-      <c r="M76" s="10" t="n"/>
-      <c r="N76" s="10" t="n"/>
-      <c r="O76" s="10" t="n"/>
-      <c r="P76" s="10" t="n"/>
-      <c r="Q76" s="10" t="n"/>
-      <c r="R76" s="10" t="n"/>
-      <c r="S76" s="10" t="n"/>
-      <c r="T76" s="10" t="n"/>
-      <c r="U76" s="10" t="n"/>
-      <c r="V76" s="10" t="n"/>
-      <c r="W76" s="10" t="n"/>
-      <c r="X76" s="10" t="n"/>
-      <c r="Y76" s="10" t="n"/>
-      <c r="Z76" s="10" t="n"/>
-      <c r="AA76" s="10" t="n"/>
-      <c r="AB76" s="10" t="n"/>
-      <c r="AC76" s="10" t="n"/>
-      <c r="AD76" s="10" t="n"/>
-      <c r="AE76" s="10" t="n"/>
-      <c r="AF76" s="10" t="n"/>
-      <c r="AG76" s="10" t="n"/>
-      <c r="AH76" s="10" t="n"/>
-      <c r="AI76" s="10" t="n"/>
-      <c r="AJ76" s="10" t="n"/>
-      <c r="AK76" s="11" t="n"/>
-    </row>
-    <row r="78" ht="19.5" customHeight="1">
-      <c r="B78" s="40" t="inlineStr">
+      <c r="D77" s="10" t="n"/>
+      <c r="E77" s="10" t="n"/>
+      <c r="F77" s="10" t="n"/>
+      <c r="G77" s="10" t="n"/>
+      <c r="H77" s="10" t="n"/>
+      <c r="I77" s="10" t="n"/>
+      <c r="J77" s="10" t="n"/>
+      <c r="K77" s="10" t="n"/>
+      <c r="L77" s="10" t="n"/>
+      <c r="M77" s="10" t="n"/>
+      <c r="N77" s="10" t="n"/>
+      <c r="O77" s="10" t="n"/>
+      <c r="P77" s="10" t="n"/>
+      <c r="Q77" s="10" t="n"/>
+      <c r="R77" s="10" t="n"/>
+      <c r="S77" s="10" t="n"/>
+      <c r="T77" s="10" t="n"/>
+      <c r="U77" s="10" t="n"/>
+      <c r="V77" s="10" t="n"/>
+      <c r="W77" s="10" t="n"/>
+      <c r="X77" s="10" t="n"/>
+      <c r="Y77" s="10" t="n"/>
+      <c r="Z77" s="10" t="n"/>
+      <c r="AA77" s="10" t="n"/>
+      <c r="AB77" s="10" t="n"/>
+      <c r="AC77" s="10" t="n"/>
+      <c r="AD77" s="10" t="n"/>
+      <c r="AE77" s="10" t="n"/>
+      <c r="AF77" s="10" t="n"/>
+      <c r="AG77" s="10" t="n"/>
+      <c r="AH77" s="10" t="n"/>
+      <c r="AI77" s="10" t="n"/>
+      <c r="AJ77" s="10" t="n"/>
+      <c r="AK77" s="11" t="n"/>
+    </row>
+    <row r="79" ht="19.5" customHeight="1">
+      <c r="B79" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="72" customHeight="1">
-      <c r="C79" s="19" t="inlineStr">
+    <row r="80" ht="72" customHeight="1">
+      <c r="C80" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -7159,50 +7421,50 @@
 }</t>
         </is>
       </c>
-      <c r="D79" s="10" t="n"/>
-      <c r="E79" s="10" t="n"/>
-      <c r="F79" s="10" t="n"/>
-      <c r="G79" s="10" t="n"/>
-      <c r="H79" s="10" t="n"/>
-      <c r="I79" s="10" t="n"/>
-      <c r="J79" s="10" t="n"/>
-      <c r="K79" s="10" t="n"/>
-      <c r="L79" s="10" t="n"/>
-      <c r="M79" s="10" t="n"/>
-      <c r="N79" s="10" t="n"/>
-      <c r="O79" s="10" t="n"/>
-      <c r="P79" s="10" t="n"/>
-      <c r="Q79" s="10" t="n"/>
-      <c r="R79" s="10" t="n"/>
-      <c r="S79" s="10" t="n"/>
-      <c r="T79" s="10" t="n"/>
-      <c r="U79" s="10" t="n"/>
-      <c r="V79" s="10" t="n"/>
-      <c r="W79" s="10" t="n"/>
-      <c r="X79" s="10" t="n"/>
-      <c r="Y79" s="10" t="n"/>
-      <c r="Z79" s="10" t="n"/>
-      <c r="AA79" s="10" t="n"/>
-      <c r="AB79" s="10" t="n"/>
-      <c r="AC79" s="10" t="n"/>
-      <c r="AD79" s="10" t="n"/>
-      <c r="AE79" s="10" t="n"/>
-      <c r="AF79" s="10" t="n"/>
-      <c r="AG79" s="10" t="n"/>
-      <c r="AH79" s="10" t="n"/>
-      <c r="AI79" s="10" t="n"/>
-      <c r="AJ79" s="10" t="n"/>
-      <c r="AK79" s="11" t="n"/>
-    </row>
-    <row r="81" ht="19.5" customHeight="1">
-      <c r="B81" s="40" t="inlineStr">
+      <c r="D80" s="10" t="n"/>
+      <c r="E80" s="10" t="n"/>
+      <c r="F80" s="10" t="n"/>
+      <c r="G80" s="10" t="n"/>
+      <c r="H80" s="10" t="n"/>
+      <c r="I80" s="10" t="n"/>
+      <c r="J80" s="10" t="n"/>
+      <c r="K80" s="10" t="n"/>
+      <c r="L80" s="10" t="n"/>
+      <c r="M80" s="10" t="n"/>
+      <c r="N80" s="10" t="n"/>
+      <c r="O80" s="10" t="n"/>
+      <c r="P80" s="10" t="n"/>
+      <c r="Q80" s="10" t="n"/>
+      <c r="R80" s="10" t="n"/>
+      <c r="S80" s="10" t="n"/>
+      <c r="T80" s="10" t="n"/>
+      <c r="U80" s="10" t="n"/>
+      <c r="V80" s="10" t="n"/>
+      <c r="W80" s="10" t="n"/>
+      <c r="X80" s="10" t="n"/>
+      <c r="Y80" s="10" t="n"/>
+      <c r="Z80" s="10" t="n"/>
+      <c r="AA80" s="10" t="n"/>
+      <c r="AB80" s="10" t="n"/>
+      <c r="AC80" s="10" t="n"/>
+      <c r="AD80" s="10" t="n"/>
+      <c r="AE80" s="10" t="n"/>
+      <c r="AF80" s="10" t="n"/>
+      <c r="AG80" s="10" t="n"/>
+      <c r="AH80" s="10" t="n"/>
+      <c r="AI80" s="10" t="n"/>
+      <c r="AJ80" s="10" t="n"/>
+      <c r="AK80" s="11" t="n"/>
+    </row>
+    <row r="82" ht="19.5" customHeight="1">
+      <c r="B82" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="72" customHeight="1">
-      <c r="C82" s="19" t="inlineStr">
+    <row r="83" ht="72" customHeight="1">
+      <c r="C83" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -7210,408 +7472,429 @@
 }</t>
         </is>
       </c>
-      <c r="D82" s="10" t="n"/>
-      <c r="E82" s="10" t="n"/>
-      <c r="F82" s="10" t="n"/>
-      <c r="G82" s="10" t="n"/>
-      <c r="H82" s="10" t="n"/>
-      <c r="I82" s="10" t="n"/>
-      <c r="J82" s="10" t="n"/>
-      <c r="K82" s="10" t="n"/>
-      <c r="L82" s="10" t="n"/>
-      <c r="M82" s="10" t="n"/>
-      <c r="N82" s="10" t="n"/>
-      <c r="O82" s="10" t="n"/>
-      <c r="P82" s="10" t="n"/>
-      <c r="Q82" s="10" t="n"/>
-      <c r="R82" s="10" t="n"/>
-      <c r="S82" s="10" t="n"/>
-      <c r="T82" s="10" t="n"/>
-      <c r="U82" s="10" t="n"/>
-      <c r="V82" s="10" t="n"/>
-      <c r="W82" s="10" t="n"/>
-      <c r="X82" s="10" t="n"/>
-      <c r="Y82" s="10" t="n"/>
-      <c r="Z82" s="10" t="n"/>
-      <c r="AA82" s="10" t="n"/>
-      <c r="AB82" s="10" t="n"/>
-      <c r="AC82" s="10" t="n"/>
-      <c r="AD82" s="10" t="n"/>
-      <c r="AE82" s="10" t="n"/>
-      <c r="AF82" s="10" t="n"/>
-      <c r="AG82" s="10" t="n"/>
-      <c r="AH82" s="10" t="n"/>
-      <c r="AI82" s="10" t="n"/>
-      <c r="AJ82" s="10" t="n"/>
-      <c r="AK82" s="11" t="n"/>
-    </row>
-    <row r="84" ht="19.5" customHeight="1"/>
-    <row r="85" ht="19.5" customHeight="1">
-      <c r="A85" s="27" t="inlineStr">
+      <c r="D83" s="10" t="n"/>
+      <c r="E83" s="10" t="n"/>
+      <c r="F83" s="10" t="n"/>
+      <c r="G83" s="10" t="n"/>
+      <c r="H83" s="10" t="n"/>
+      <c r="I83" s="10" t="n"/>
+      <c r="J83" s="10" t="n"/>
+      <c r="K83" s="10" t="n"/>
+      <c r="L83" s="10" t="n"/>
+      <c r="M83" s="10" t="n"/>
+      <c r="N83" s="10" t="n"/>
+      <c r="O83" s="10" t="n"/>
+      <c r="P83" s="10" t="n"/>
+      <c r="Q83" s="10" t="n"/>
+      <c r="R83" s="10" t="n"/>
+      <c r="S83" s="10" t="n"/>
+      <c r="T83" s="10" t="n"/>
+      <c r="U83" s="10" t="n"/>
+      <c r="V83" s="10" t="n"/>
+      <c r="W83" s="10" t="n"/>
+      <c r="X83" s="10" t="n"/>
+      <c r="Y83" s="10" t="n"/>
+      <c r="Z83" s="10" t="n"/>
+      <c r="AA83" s="10" t="n"/>
+      <c r="AB83" s="10" t="n"/>
+      <c r="AC83" s="10" t="n"/>
+      <c r="AD83" s="10" t="n"/>
+      <c r="AE83" s="10" t="n"/>
+      <c r="AF83" s="10" t="n"/>
+      <c r="AG83" s="10" t="n"/>
+      <c r="AH83" s="10" t="n"/>
+      <c r="AI83" s="10" t="n"/>
+      <c r="AJ83" s="10" t="n"/>
+      <c r="AK83" s="11" t="n"/>
+    </row>
+    <row r="85" ht="19.5" customHeight="1"/>
+    <row r="86" ht="19.5" customHeight="1">
+      <c r="A86" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="B86" s="27" t="inlineStr">
+    <row r="87" ht="18" customHeight="1">
+      <c r="B87" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="C87" s="41" t="inlineStr">
+    <row r="88" ht="18" customHeight="1">
+      <c r="C88" s="41" t="inlineStr">
         <is>
           <t>クエリパラメータの検証：</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="18" customHeight="1">
-      <c r="D88" s="41" t="inlineStr">
-        <is>
-          <t>kumiaiin_code：最大20桁</t>
         </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="D89" s="41" t="inlineStr">
         <is>
-          <t>shimei：最大100桁</t>
+          <t>kumiaiin_code：最大20桁</t>
         </is>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="D90" s="41" t="inlineStr">
         <is>
-          <t>shimei_kana：最大200桁</t>
+          <t>shimei：最大100桁</t>
         </is>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="D91" s="41" t="inlineStr">
         <is>
+          <t>shimei_kana：最大200桁</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="D92" s="41" t="inlineStr">
+        <is>
           <t>haitatsu_address：最大300桁</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="36" customHeight="1">
-      <c r="D92" s="41" t="inlineStr">
+    <row r="93" ht="36" customHeight="1">
+      <c r="D93" s="41" t="inlineStr">
         <is>
           <t>dokusya_kaishi_date_from / dokusya_kaishi_date_to：YYYY-MM-DD 形式</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="18" customHeight="1">
-      <c r="D93" s="41" t="inlineStr">
-        <is>
-          <t>page：1以上</t>
         </is>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="D94" s="41" t="inlineStr">
         <is>
+          <t>page：1以上</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="D95" s="41" t="inlineStr">
+        <is>
           <t>per_page：1〜100</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="36" customHeight="1">
-      <c r="D95" s="41" t="inlineStr">
+    <row r="96" ht="36" customHeight="1">
+      <c r="D96" s="41" t="inlineStr">
         <is>
           <t>sort_by：許可カラム（`kanri_shiten_name` / `shiten_name` / `kumiaiin_code` / `hanbaiten_code`）に含まれるか確認</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="18" customHeight="1">
-      <c r="D96" s="41" t="inlineStr">
+    <row r="97" ht="18" customHeight="1">
+      <c r="D97" s="41" t="inlineStr">
         <is>
           <t>sort_order：`asc` または `desc`</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="36" customHeight="1">
-      <c r="C97" s="41" t="inlineStr">
+    <row r="98" ht="36" customHeight="1">
+      <c r="C98" s="41" t="inlineStr">
         <is>
           <t>デフォルト値を設定する（page=1, per_page=20, sort_by=kumiaiin_code, sort_order=asc）</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="18" customHeight="1">
-      <c r="C98" s="41" t="inlineStr">
+    <row r="99" ht="18" customHeight="1">
+      <c r="C99" s="41" t="inlineStr">
         <is>
           <t>不正なパラメータの場合：HTTP 400 (`VALIDATION_ERROR`)</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="18" customHeight="1">
-      <c r="B99" s="27" t="inlineStr">
+    <row r="100" ht="18" customHeight="1">
+      <c r="B100" s="27" t="inlineStr">
         <is>
           <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="18" customHeight="1">
-      <c r="C100" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="C101" s="41" t="inlineStr">
         <is>
-          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
       <c r="C102" s="41" t="inlineStr">
         <is>
+          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="C103" s="41" t="inlineStr">
+        <is>
           <t>必要権限: `dokusya.replace_hanbaiten`</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="36" customHeight="1">
-      <c r="C103" s="41" t="inlineStr">
+    <row r="104" ht="36" customHeight="1">
+      <c r="C104" s="41" t="inlineStr">
         <is>
           <t>該当権限保持ロール: CHUOKAI（中央会）/ JA_HONTEN（JA本店）/ JA_KANRI_SHITEN（JA管理支店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="C104" s="41" t="inlineStr">
-        <is>
-          <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
         </is>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
       <c r="C105" s="41" t="inlineStr">
         <is>
+          <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="C106" s="41" t="inlineStr">
+        <is>
           <t>DataScope:</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="36" customHeight="1">
-      <c r="D106" s="41" t="inlineStr">
+    <row r="107" ht="36" customHeight="1">
+      <c r="D107" s="41" t="inlineStr">
         <is>
           <t>中央会：自中央会配下のJAに紐づく購読者のみ参照可（`d.ja_id IN (中央会のJA一覧)` または `mj.chuokai_id = :user_chuokai_id`）</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="D107" s="41" t="inlineStr">
+    <row r="108" ht="18" customHeight="1">
+      <c r="D108" s="41" t="inlineStr">
         <is>
           <t>JA本店：自JAのみ参照可（`d.ja_id = :user_ja_id`）</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="36" customHeight="1">
-      <c r="D108" s="41" t="inlineStr">
+    <row r="109" ht="36" customHeight="1">
+      <c r="D109" s="41" t="inlineStr">
         <is>
           <t>JA管理支店：自管理支店配下の購読者のみ参照可（`d.kanri_shiten_id = :user_kanri_shiten_id`）</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="36" customHeight="1">
-      <c r="C109" s="41" t="inlineStr">
+    <row r="110" ht="36" customHeight="1">
+      <c r="C110" s="41" t="inlineStr">
         <is>
           <t>DataScope違反（他JA・他管理支店のレコードへのアクセス）の場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="18" customHeight="1">
-      <c r="B110" s="27" t="inlineStr">
+    <row r="111" ht="18" customHeight="1">
+      <c r="B111" s="27" t="inlineStr">
         <is>
           <t>4.3 データ取得条件の設定</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="72" customHeight="1">
-      <c r="C111" s="41" t="inlineStr">
+    <row r="112" ht="72" customHeight="1">
+      <c r="C112" s="41" t="inlineStr">
         <is>
           <t>**入力チェック（購読種別・必須）**：`dokusya_shubetsu` は必須で **1:紙版 / 2:電子版 のみ**。未入力・3(併読)・範囲外は HTTP 400 (`VALIDATION_ERROR`, `{ field: "dokusya_shubetsu", message: "購読種別は紙版または電子版で指定してください。" }`)。</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="90" customHeight="1">
-      <c r="C112" s="41" t="inlineStr">
+    <row r="113" ht="90" customHeight="1">
+      <c r="C113" s="41" t="inlineStr">
         <is>
           <t>**入力チェック（適用日・種別依存／顧客要件 2026-07 改訂）**：`joho_henko_tekiyo_date` は必須。未入力は HTTP 400 (`VALIDATION_ERROR`, `適用日を入力してください。`)、形式（YYYY-MM-DD）不正も 400。日付ルールは `dokusya_shubetsu` 依存で判定する（当日判定は `todayIsoJst()` = Asia/Tokyo、置換実行 API と同一基準）：</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="36" customHeight="1">
-      <c r="D113" s="41" t="inlineStr">
+    <row r="114" ht="36" customHeight="1">
+      <c r="D114" s="41" t="inlineStr">
         <is>
           <t>**紙版(1)**：**未来日のみ**（`&gt; 当日`）。当日以下は HTTP 400 (`DATE_RANGE_INVALID`, `紙版の適用日は本日より後の日付を入力してください。`)。</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="108" customHeight="1">
-      <c r="D114" s="41" t="inlineStr">
+    <row r="115" ht="108" customHeight="1">
+      <c r="D115" s="41" t="inlineStr">
         <is>
           <t>**電子版(2)**：**本画面（販売店一括置換）の対象外**。日付に関係なく HTTP 400 (`VALIDATION_ERROR`, `{ field: "dokusya_shubetsu", message: "電子版は本画面では対象外です。" }`／ACSMS-MSG-015-009)。電子版=電子配信で販売店を持たないため一括置換できない（顧客要件 2026-07 改訂で「電子版=当日置換」を撤回）。UI は電子版選択時にトーストでこのメッセージを通知し検索ボタンを非活性化する（インラインメッセージは表示しない）。</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="36" customHeight="1">
-      <c r="C115" s="41" t="inlineStr">
+    <row r="116" ht="36" customHeight="1">
+      <c r="C116" s="41" t="inlineStr">
         <is>
           <t>ログインユーザーのスコープ（role_code, ja_id, kanri_shiten_id）を取得する。</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="18" customHeight="1">
-      <c r="C116" s="41" t="inlineStr">
+    <row r="117" ht="18" customHeight="1">
+      <c r="C117" s="41" t="inlineStr">
         <is>
           <t>DataScope を role_code により適用する（4.2 参照）。</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="36" customHeight="1">
-      <c r="C117" s="41" t="inlineStr">
+    <row r="118" ht="36" customHeight="1">
+      <c r="C118" s="41" t="inlineStr">
         <is>
           <t>**購読種別の絞り込み（顧客要件 2026-07）**：`d.dokusya_shubetsu = :dokusya_shubetsu`（必須・1 or 2）で対象種別のみに絞る。</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="72" customHeight="1">
-      <c r="C118" s="41" t="inlineStr">
-        <is>
-          <t>**置換可能条件（顧客要件 2026-07）**：指定した `joho_henko_tekiyo_date`（適用日）時点で置換可能な購読者のみに絞り込む。置換実行 API の集約チェック（`assertReplaceTekiyoDate`）と同一境界を per-row で適用するため、返却された任意の部分集合を選択しても実行時チェックが必ず通る：</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="36" customHeight="1">
-      <c r="D119" s="41" t="inlineStr">
-        <is>
-          <t>`d.dokusya_kaishi_date &lt;= :joho_henko_tekiyo_date`（購読開始日が適用日以前）</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="54" customHeight="1">
+    <row r="119" ht="108" customHeight="1">
+      <c r="C119" s="41" t="inlineStr">
+        <is>
+          <t>**置換可能条件（顧客要件 2026-07 改訂・as-of 適用日）**：現行 master ではなく、各購読者の「適用日時点で有効な履歴レコード」で置換元販売店・購読状態を判定する。有効レコード = `t_dokusya_rireki` のうち `joho_henko_tekiyo_date ≦ :joho_henko_tekiyo_date` かつ `joho_henko_tekiyo_date` が最大（同日は `rireki_no` 最大）の行（`DISTINCT ON (dokusya_id)`）。その有効レコードが次を満たす購読者のみ返す：</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="36" customHeight="1">
       <c r="D120" s="41" t="inlineStr">
         <is>
-          <t>`(d.dokusya_chushi_date IS NULL OR d.dokusya_chushi_date &gt; :joho_henko_tekiyo_date)`（解約予定日が無い、または適用日より後）</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="18" customHeight="1">
-      <c r="C121" s="41" t="inlineStr">
-        <is>
-          <t>検索条件を追加する：</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="36" customHeight="1">
+          <t>`eff.hanbaiten_id &lt;&gt; :new_hanbaiten_id`（既に置換先を配達している購読者を除外・必須）</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="54" customHeight="1">
+      <c r="D121" s="41" t="inlineStr">
+        <is>
+          <t>`hanbaiten_id`（配達販売店）を指定した場合のみ追加：`eff.hanbaiten_id = :hanbaiten_id`（適用日時点の配達販売店 = 指定値）。配達販売店 = 置換先 のときは 0 件</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="18" customHeight="1">
       <c r="D122" s="41" t="inlineStr">
         <is>
-          <t>kanri_shiten_id 指定時：`d.kanri_shiten_id = :kanri_shiten_id`</t>
+          <t>`eff.tetsuzuki_shurui = 1`（購読中）</t>
         </is>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
       <c r="D123" s="41" t="inlineStr">
         <is>
-          <t>shiten_id 指定時：`d.shiten_id = :shiten_id`</t>
+          <t>`eff.dokusya_shubetsu = :dokusya_shubetsu`（指定種別）</t>
         </is>
       </c>
     </row>
     <row r="124" ht="36" customHeight="1">
       <c r="D124" s="41" t="inlineStr">
         <is>
-          <t>kumiaiin_code 指定時：`d.kumiaiin_code = :kumiaiin_code`（完全一致）</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="36" customHeight="1">
+          <t>`eff.dokusya_kaishi_date &lt;= :joho_henko_tekiyo_date`（購読開始日が適用日以前）</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="54" customHeight="1">
       <c r="D125" s="41" t="inlineStr">
         <is>
-          <t>shimei 指定時：`CONCAT(d.shimei_sei, d.shimei_mei) LIKE :shimei_like`（部分一致）</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="36" customHeight="1">
+          <t>`(eff.dokusya_chushi_date IS NULL OR eff.dokusya_chushi_date &gt; :joho_henko_tekiyo_date)`（解約予定日が無い、または適用日より後）</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="54" customHeight="1">
       <c r="D126" s="41" t="inlineStr">
         <is>
-          <t>shimei_kana 指定時：`CONCAT(d.shimei_kana_sei, d.shimei_kana_mei) LIKE :shimei_kana_like`（部分一致）</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="54" customHeight="1">
-      <c r="D127" s="41" t="inlineStr">
-        <is>
-          <t>haitatsu_address 指定時：`CONCAT(t.todofuken_name, d.haitatsu_shikuchoson, d.haitatsu_chome_banchi, d.haitatsu_tatemono_mei) LIKE :haitatsu_like`（部分一致）</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="18" customHeight="1">
+          <t>未来の適用日でも、その時点で有効な履歴で判定するため、現行 master の販売店が既に変わっていても正しい母集合を返す。表示・DataScope・その他検索条件は master(`d`) 側で適用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="18" customHeight="1">
+      <c r="C127" s="41" t="inlineStr">
+        <is>
+          <t>検索条件を追加する：</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="36" customHeight="1">
       <c r="D128" s="41" t="inlineStr">
         <is>
-          <t>hanbaiten_id 指定時：`d.hanbaiten_id = :hanbaiten_id`</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="36" customHeight="1">
+          <t>kanri_shiten_id 指定時：`d.kanri_shiten_id = :kanri_shiten_id`</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="18" customHeight="1">
       <c r="D129" s="41" t="inlineStr">
         <is>
-          <t>dokusya_kaishi_date_from 指定時：`d.shoki_dokusya_kaishi_date &gt;= :date_from`</t>
+          <t>shiten_id 指定時：`d.shiten_id = :shiten_id`</t>
         </is>
       </c>
     </row>
     <row r="130" ht="36" customHeight="1">
       <c r="D130" s="41" t="inlineStr">
         <is>
-          <t>dokusya_kaishi_date_to 指定時：`d.shoki_dokusya_kaishi_date &lt;= :date_to`</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="18" customHeight="1">
-      <c r="C131" s="41" t="inlineStr">
-        <is>
-          <t>固定条件：</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="18" customHeight="1">
+          <t>kumiaiin_code 指定時：`d.kumiaiin_code = :kumiaiin_code`（完全一致）</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="36" customHeight="1">
+      <c r="D131" s="41" t="inlineStr">
+        <is>
+          <t>shimei 指定時：`CONCAT(d.shimei_sei, d.shimei_mei) LIKE :shimei_like`（部分一致）</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="36" customHeight="1">
       <c r="D132" s="41" t="inlineStr">
         <is>
-          <t>`d.tetsuzuki_shurui = 1`（購読中の購読者のみ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="18" customHeight="1">
+          <t>shimei_kana 指定時：`CONCAT(d.shimei_kana_sei, d.shimei_kana_mei) LIKE :shimei_kana_like`（部分一致）</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="54" customHeight="1">
       <c r="D133" s="41" t="inlineStr">
         <is>
-          <t>`d.deleted_at IS NULL`（論理削除除外）</t>
+          <t>haitatsu_address 指定時：`CONCAT(t.todofuken_name, d.haitatsu_shikuchoson, d.haitatsu_chome_banchi, d.haitatsu_tatemono_mei) LIKE :haitatsu_like`（部分一致）</t>
         </is>
       </c>
     </row>
     <row r="134" ht="36" customHeight="1">
       <c r="D134" s="41" t="inlineStr">
         <is>
-          <t>`d.dokusya_kaishi_date &lt;= :joho_henko_tekiyo_date`（置換可能条件）</t>
+          <t>hanbaiten_id（置換元・必須）：master ではなく上記 as-of 有効レコードの `eff.hanbaiten_id = :hanbaiten_id` で判定（§置換可能条件）</t>
         </is>
       </c>
     </row>
     <row r="135" ht="36" customHeight="1">
       <c r="D135" s="41" t="inlineStr">
         <is>
-          <t>`(d.dokusya_chushi_date IS NULL OR d.dokusya_chushi_date &gt; :joho_henko_tekiyo_date)`（置換可能条件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="18" customHeight="1">
-      <c r="B136" s="27" t="inlineStr">
+          <t>dokusya_kaishi_date_from 指定時：`d.shoki_dokusya_kaishi_date &gt;= :date_from`</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="36" customHeight="1">
+      <c r="D136" s="41" t="inlineStr">
+        <is>
+          <t>dokusya_kaishi_date_to 指定時：`d.shoki_dokusya_kaishi_date &lt;= :date_to`</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="18" customHeight="1">
+      <c r="C137" s="41" t="inlineStr">
+        <is>
+          <t>固定条件：</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="18" customHeight="1">
+      <c r="D138" s="41" t="inlineStr">
+        <is>
+          <t>`d.deleted_at IS NULL`（論理削除除外・master 側）</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="36" customHeight="1">
+      <c r="D139" s="41" t="inlineStr">
+        <is>
+          <t>`d.dokusya_id IN (…as-of 有効レコードのサブクエリ…)`（購読中/種別/適用日/置換元は上記 §置換可能条件のサブクエリで判定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="18" customHeight="1">
+      <c r="B140" s="27" t="inlineStr">
         <is>
           <t>4.4 データ件数の取得</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="396" customHeight="1">
-      <c r="C137" s="42" t="inlineStr">
+    <row r="141" ht="396" customHeight="1">
+      <c r="C141" s="42" t="inlineStr">
         <is>
           <t>SELECT COUNT(*)
 FROM t_dokusya d
@@ -7637,50 +7920,50 @@
   AND (:date_to IS NULL OR d.shoki_dokusya_kaishi_date &lt;= :date_to)</t>
         </is>
       </c>
-      <c r="D137" s="10" t="n"/>
-      <c r="E137" s="10" t="n"/>
-      <c r="F137" s="10" t="n"/>
-      <c r="G137" s="10" t="n"/>
-      <c r="H137" s="10" t="n"/>
-      <c r="I137" s="10" t="n"/>
-      <c r="J137" s="10" t="n"/>
-      <c r="K137" s="10" t="n"/>
-      <c r="L137" s="10" t="n"/>
-      <c r="M137" s="10" t="n"/>
-      <c r="N137" s="10" t="n"/>
-      <c r="O137" s="10" t="n"/>
-      <c r="P137" s="10" t="n"/>
-      <c r="Q137" s="10" t="n"/>
-      <c r="R137" s="10" t="n"/>
-      <c r="S137" s="10" t="n"/>
-      <c r="T137" s="10" t="n"/>
-      <c r="U137" s="10" t="n"/>
-      <c r="V137" s="10" t="n"/>
-      <c r="W137" s="10" t="n"/>
-      <c r="X137" s="10" t="n"/>
-      <c r="Y137" s="10" t="n"/>
-      <c r="Z137" s="10" t="n"/>
-      <c r="AA137" s="10" t="n"/>
-      <c r="AB137" s="10" t="n"/>
-      <c r="AC137" s="10" t="n"/>
-      <c r="AD137" s="10" t="n"/>
-      <c r="AE137" s="10" t="n"/>
-      <c r="AF137" s="10" t="n"/>
-      <c r="AG137" s="10" t="n"/>
-      <c r="AH137" s="10" t="n"/>
-      <c r="AI137" s="10" t="n"/>
-      <c r="AJ137" s="10" t="n"/>
-      <c r="AK137" s="11" t="n"/>
-    </row>
-    <row r="138" ht="18" customHeight="1">
-      <c r="B138" s="27" t="inlineStr">
+      <c r="D141" s="10" t="n"/>
+      <c r="E141" s="10" t="n"/>
+      <c r="F141" s="10" t="n"/>
+      <c r="G141" s="10" t="n"/>
+      <c r="H141" s="10" t="n"/>
+      <c r="I141" s="10" t="n"/>
+      <c r="J141" s="10" t="n"/>
+      <c r="K141" s="10" t="n"/>
+      <c r="L141" s="10" t="n"/>
+      <c r="M141" s="10" t="n"/>
+      <c r="N141" s="10" t="n"/>
+      <c r="O141" s="10" t="n"/>
+      <c r="P141" s="10" t="n"/>
+      <c r="Q141" s="10" t="n"/>
+      <c r="R141" s="10" t="n"/>
+      <c r="S141" s="10" t="n"/>
+      <c r="T141" s="10" t="n"/>
+      <c r="U141" s="10" t="n"/>
+      <c r="V141" s="10" t="n"/>
+      <c r="W141" s="10" t="n"/>
+      <c r="X141" s="10" t="n"/>
+      <c r="Y141" s="10" t="n"/>
+      <c r="Z141" s="10" t="n"/>
+      <c r="AA141" s="10" t="n"/>
+      <c r="AB141" s="10" t="n"/>
+      <c r="AC141" s="10" t="n"/>
+      <c r="AD141" s="10" t="n"/>
+      <c r="AE141" s="10" t="n"/>
+      <c r="AF141" s="10" t="n"/>
+      <c r="AG141" s="10" t="n"/>
+      <c r="AH141" s="10" t="n"/>
+      <c r="AI141" s="10" t="n"/>
+      <c r="AJ141" s="10" t="n"/>
+      <c r="AK141" s="11" t="n"/>
+    </row>
+    <row r="142" ht="18" customHeight="1">
+      <c r="B142" s="27" t="inlineStr">
         <is>
           <t>4.5 データ取得</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="324" customHeight="1">
-      <c r="C139" s="42" t="inlineStr">
+    <row r="143" ht="324" customHeight="1">
+      <c r="C143" s="42" t="inlineStr">
         <is>
           <t>SELECT d.dokusya_id, d.kanri_shiten_id, ks.kanri_shiten_name,
        d.shiten_id, s.shiten_name,
@@ -7702,123 +7985,130 @@
 LIMIT :per_page OFFSET (:page - 1) * :per_page</t>
         </is>
       </c>
-      <c r="D139" s="10" t="n"/>
-      <c r="E139" s="10" t="n"/>
-      <c r="F139" s="10" t="n"/>
-      <c r="G139" s="10" t="n"/>
-      <c r="H139" s="10" t="n"/>
-      <c r="I139" s="10" t="n"/>
-      <c r="J139" s="10" t="n"/>
-      <c r="K139" s="10" t="n"/>
-      <c r="L139" s="10" t="n"/>
-      <c r="M139" s="10" t="n"/>
-      <c r="N139" s="10" t="n"/>
-      <c r="O139" s="10" t="n"/>
-      <c r="P139" s="10" t="n"/>
-      <c r="Q139" s="10" t="n"/>
-      <c r="R139" s="10" t="n"/>
-      <c r="S139" s="10" t="n"/>
-      <c r="T139" s="10" t="n"/>
-      <c r="U139" s="10" t="n"/>
-      <c r="V139" s="10" t="n"/>
-      <c r="W139" s="10" t="n"/>
-      <c r="X139" s="10" t="n"/>
-      <c r="Y139" s="10" t="n"/>
-      <c r="Z139" s="10" t="n"/>
-      <c r="AA139" s="10" t="n"/>
-      <c r="AB139" s="10" t="n"/>
-      <c r="AC139" s="10" t="n"/>
-      <c r="AD139" s="10" t="n"/>
-      <c r="AE139" s="10" t="n"/>
-      <c r="AF139" s="10" t="n"/>
-      <c r="AG139" s="10" t="n"/>
-      <c r="AH139" s="10" t="n"/>
-      <c r="AI139" s="10" t="n"/>
-      <c r="AJ139" s="10" t="n"/>
-      <c r="AK139" s="11" t="n"/>
-    </row>
-    <row r="140" ht="18" customHeight="1">
-      <c r="B140" s="27" t="inlineStr">
-        <is>
-          <t>4.6 レスポンス生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="36" customHeight="1">
-      <c r="C141" s="41" t="inlineStr">
-        <is>
-          <t>`shimei` = `shimei_sei + ' ' + shimei_mei` を結合した値で返却する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="54" customHeight="1">
-      <c r="C142" s="41" t="inlineStr">
-        <is>
-          <t>`haitatsu_address` = `todofuken_name + haitatsu_shikuchoson + haitatsu_chome_banchi + haitatsu_tatemono_mei` を結合した値で返却する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="18" customHeight="1">
-      <c r="C143" s="41" t="inlineStr">
-        <is>
-          <t>data 配列と meta オブジェクトを含む JSON を返却する。HTTP 200。</t>
-        </is>
-      </c>
+      <c r="D143" s="10" t="n"/>
+      <c r="E143" s="10" t="n"/>
+      <c r="F143" s="10" t="n"/>
+      <c r="G143" s="10" t="n"/>
+      <c r="H143" s="10" t="n"/>
+      <c r="I143" s="10" t="n"/>
+      <c r="J143" s="10" t="n"/>
+      <c r="K143" s="10" t="n"/>
+      <c r="L143" s="10" t="n"/>
+      <c r="M143" s="10" t="n"/>
+      <c r="N143" s="10" t="n"/>
+      <c r="O143" s="10" t="n"/>
+      <c r="P143" s="10" t="n"/>
+      <c r="Q143" s="10" t="n"/>
+      <c r="R143" s="10" t="n"/>
+      <c r="S143" s="10" t="n"/>
+      <c r="T143" s="10" t="n"/>
+      <c r="U143" s="10" t="n"/>
+      <c r="V143" s="10" t="n"/>
+      <c r="W143" s="10" t="n"/>
+      <c r="X143" s="10" t="n"/>
+      <c r="Y143" s="10" t="n"/>
+      <c r="Z143" s="10" t="n"/>
+      <c r="AA143" s="10" t="n"/>
+      <c r="AB143" s="10" t="n"/>
+      <c r="AC143" s="10" t="n"/>
+      <c r="AD143" s="10" t="n"/>
+      <c r="AE143" s="10" t="n"/>
+      <c r="AF143" s="10" t="n"/>
+      <c r="AG143" s="10" t="n"/>
+      <c r="AH143" s="10" t="n"/>
+      <c r="AI143" s="10" t="n"/>
+      <c r="AJ143" s="10" t="n"/>
+      <c r="AK143" s="11" t="n"/>
     </row>
     <row r="144" ht="18" customHeight="1">
       <c r="B144" s="27" t="inlineStr">
         <is>
+          <t>4.6 レスポンス生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="36" customHeight="1">
+      <c r="C145" s="41" t="inlineStr">
+        <is>
+          <t>`shimei` = `shimei_sei + ' ' + shimei_mei` を結合した値で返却する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="54" customHeight="1">
+      <c r="C146" s="41" t="inlineStr">
+        <is>
+          <t>`haitatsu_address` = `todofuken_name + haitatsu_shikuchoson + haitatsu_chome_banchi + haitatsu_tatemono_mei` を結合した値で返却する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="18" customHeight="1">
+      <c r="C147" s="41" t="inlineStr">
+        <is>
+          <t>data 配列と meta オブジェクトを含む JSON を返却する。HTTP 200。</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="18" customHeight="1">
+      <c r="B148" s="27" t="inlineStr">
+        <is>
           <t>4.7 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="18" customHeight="1">
-      <c r="C145" s="41" t="inlineStr">
+    <row r="149" ht="18" customHeight="1">
+      <c r="C149" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="357">
+  <mergeCells count="367">
     <mergeCell ref="D134:AK134"/>
     <mergeCell ref="T24:X24"/>
     <mergeCell ref="Y45:AE45"/>
     <mergeCell ref="D61:L61"/>
     <mergeCell ref="D48:L48"/>
     <mergeCell ref="T53:X53"/>
+    <mergeCell ref="D62:L62"/>
     <mergeCell ref="D56:L56"/>
+    <mergeCell ref="B87:AK87"/>
     <mergeCell ref="T55:X55"/>
     <mergeCell ref="M59:P59"/>
+    <mergeCell ref="C113:AK113"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="C100:AK100"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
+    <mergeCell ref="C65:AK65"/>
+    <mergeCell ref="B73:I73"/>
     <mergeCell ref="D51:L51"/>
-    <mergeCell ref="C142:AK142"/>
     <mergeCell ref="B10:I10"/>
+    <mergeCell ref="C80:AK80"/>
     <mergeCell ref="AF22:AK22"/>
     <mergeCell ref="Q25:S25"/>
     <mergeCell ref="M54:P54"/>
+    <mergeCell ref="C44:C57"/>
     <mergeCell ref="D124:AK124"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="B138:AK138"/>
     <mergeCell ref="Y34:AB34"/>
     <mergeCell ref="T37:X37"/>
+    <mergeCell ref="B76:I76"/>
     <mergeCell ref="Y25:AB25"/>
     <mergeCell ref="D126:AK126"/>
     <mergeCell ref="B140:AK140"/>
     <mergeCell ref="Y36:AB36"/>
-    <mergeCell ref="C131:AK131"/>
+    <mergeCell ref="T38:X38"/>
     <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="C38:L38"/>
     <mergeCell ref="Q59:S59"/>
     <mergeCell ref="Q22:S22"/>
     <mergeCell ref="Q46:S46"/>
+    <mergeCell ref="C88:AK88"/>
     <mergeCell ref="Y53:AE53"/>
     <mergeCell ref="D129:AK129"/>
-    <mergeCell ref="AF41:AK41"/>
     <mergeCell ref="Q61:S61"/>
+    <mergeCell ref="A40:AK40"/>
     <mergeCell ref="AF35:AK35"/>
     <mergeCell ref="C33:L33"/>
     <mergeCell ref="Q48:S48"/>
@@ -7826,11 +8116,11 @@
     <mergeCell ref="Y55:AE55"/>
     <mergeCell ref="C117:AK117"/>
     <mergeCell ref="C35:L35"/>
-    <mergeCell ref="C115:AK115"/>
+    <mergeCell ref="D139:AK139"/>
+    <mergeCell ref="B64:I64"/>
     <mergeCell ref="M27:P27"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="Q35:S35"/>
-    <mergeCell ref="C58:C61"/>
     <mergeCell ref="C145:AK145"/>
     <mergeCell ref="T45:X45"/>
     <mergeCell ref="A5:AK5"/>
@@ -7838,7 +8128,6 @@
     <mergeCell ref="AF30:AK30"/>
     <mergeCell ref="Q34:S34"/>
     <mergeCell ref="C28:L28"/>
-    <mergeCell ref="Y41:AE41"/>
     <mergeCell ref="D92:AK92"/>
     <mergeCell ref="AC25:AE25"/>
     <mergeCell ref="B11:I11"/>
@@ -7856,17 +8145,18 @@
     <mergeCell ref="AF56:AK56"/>
     <mergeCell ref="AF43:AK43"/>
     <mergeCell ref="AH1:AK1"/>
-    <mergeCell ref="C41:L41"/>
+    <mergeCell ref="Q62:S62"/>
+    <mergeCell ref="C119:AK119"/>
     <mergeCell ref="D120:AK120"/>
+    <mergeCell ref="C43:L43"/>
     <mergeCell ref="Q54:S54"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="AF57:AK57"/>
-    <mergeCell ref="M41:P41"/>
-    <mergeCell ref="A85:AK85"/>
     <mergeCell ref="M24:P24"/>
+    <mergeCell ref="B111:AK111"/>
     <mergeCell ref="T35:X35"/>
     <mergeCell ref="Y23:AB23"/>
-    <mergeCell ref="D58:L58"/>
+    <mergeCell ref="C147:AK147"/>
     <mergeCell ref="Q57:S57"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="C29:L29"/>
@@ -7874,6 +8164,7 @@
     <mergeCell ref="Y51:AE51"/>
     <mergeCell ref="D108:AK108"/>
     <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C71:AK71"/>
     <mergeCell ref="D95:AK95"/>
     <mergeCell ref="AC28:AE28"/>
     <mergeCell ref="M30:P30"/>
@@ -7881,21 +8172,24 @@
     <mergeCell ref="Q52:S52"/>
     <mergeCell ref="M46:P46"/>
     <mergeCell ref="M37:P37"/>
+    <mergeCell ref="D97:AK97"/>
     <mergeCell ref="AC30:AE30"/>
     <mergeCell ref="M61:P61"/>
     <mergeCell ref="AC23:AE23"/>
     <mergeCell ref="C102:AK102"/>
+    <mergeCell ref="C77:AK77"/>
     <mergeCell ref="J18:M18"/>
-    <mergeCell ref="C57:L57"/>
+    <mergeCell ref="C68:AK68"/>
+    <mergeCell ref="D121:AK121"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="M56:P56"/>
     <mergeCell ref="C141:AK141"/>
-    <mergeCell ref="D113:AK113"/>
     <mergeCell ref="M43:P43"/>
     <mergeCell ref="AF23:AK23"/>
     <mergeCell ref="AF50:AK50"/>
     <mergeCell ref="C42:L42"/>
     <mergeCell ref="C143:AK143"/>
+    <mergeCell ref="D115:AK115"/>
     <mergeCell ref="AF52:AK52"/>
     <mergeCell ref="T22:X22"/>
     <mergeCell ref="AF34:AK34"/>
@@ -7905,13 +8199,16 @@
     <mergeCell ref="Q58:S58"/>
     <mergeCell ref="AF44:AK44"/>
     <mergeCell ref="Q60:S60"/>
+    <mergeCell ref="M62:P62"/>
     <mergeCell ref="C32:L32"/>
     <mergeCell ref="AC29:AE29"/>
     <mergeCell ref="AF55:AK55"/>
+    <mergeCell ref="C74:AK74"/>
     <mergeCell ref="AC31:AE31"/>
     <mergeCell ref="C103:AK103"/>
     <mergeCell ref="C118:AK118"/>
     <mergeCell ref="M51:P51"/>
+    <mergeCell ref="D131:AK131"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="AF37:AK37"/>
     <mergeCell ref="AF24:AK24"/>
@@ -7919,20 +8216,15 @@
     <mergeCell ref="AF53:AK53"/>
     <mergeCell ref="D49:L49"/>
     <mergeCell ref="T48:X48"/>
-    <mergeCell ref="B66:I66"/>
-    <mergeCell ref="C87:AK87"/>
     <mergeCell ref="C98:AK98"/>
     <mergeCell ref="A20:AK20"/>
     <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="C116:AK116"/>
-    <mergeCell ref="C64:AK64"/>
     <mergeCell ref="M34:P34"/>
+    <mergeCell ref="B67:I67"/>
     <mergeCell ref="M49:P49"/>
-    <mergeCell ref="B69:I69"/>
     <mergeCell ref="Y30:AB30"/>
-    <mergeCell ref="D119:AK119"/>
     <mergeCell ref="D54:L54"/>
-    <mergeCell ref="T41:X41"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="Y29:AB29"/>
     <mergeCell ref="J9:AK9"/>
@@ -7943,23 +8235,23 @@
     <mergeCell ref="Y31:AB31"/>
     <mergeCell ref="T36:X36"/>
     <mergeCell ref="Y46:AE46"/>
-    <mergeCell ref="C111:AK111"/>
+    <mergeCell ref="D57:L57"/>
     <mergeCell ref="Y61:AE61"/>
+    <mergeCell ref="C83:AK83"/>
     <mergeCell ref="Y48:AE48"/>
     <mergeCell ref="D130:AK130"/>
     <mergeCell ref="T25:X25"/>
     <mergeCell ref="M58:P58"/>
+    <mergeCell ref="B148:AK148"/>
+    <mergeCell ref="T62:X62"/>
     <mergeCell ref="D132:AK132"/>
     <mergeCell ref="AC27:AE27"/>
     <mergeCell ref="C137:AK137"/>
     <mergeCell ref="D50:L50"/>
     <mergeCell ref="D44:L44"/>
-    <mergeCell ref="C139:AK139"/>
     <mergeCell ref="D60:L60"/>
-    <mergeCell ref="B110:AK110"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="M22:P22"/>
-    <mergeCell ref="C76:AK76"/>
     <mergeCell ref="Y59:AE59"/>
     <mergeCell ref="D45:L45"/>
     <mergeCell ref="M42:P42"/>
@@ -7970,15 +8262,18 @@
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
     <mergeCell ref="T33:X33"/>
-    <mergeCell ref="B72:I72"/>
     <mergeCell ref="D122:AK122"/>
     <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="B136:AK136"/>
+    <mergeCell ref="AC38:AE38"/>
     <mergeCell ref="Y32:AB32"/>
     <mergeCell ref="J12:AK12"/>
+    <mergeCell ref="B70:I70"/>
     <mergeCell ref="C34:L34"/>
     <mergeCell ref="C112:AK112"/>
-    <mergeCell ref="C109:AK109"/>
+    <mergeCell ref="B82:I82"/>
+    <mergeCell ref="Y62:AE62"/>
+    <mergeCell ref="D138:AK138"/>
+    <mergeCell ref="C127:AK127"/>
     <mergeCell ref="Y54:AE54"/>
     <mergeCell ref="M35:P35"/>
     <mergeCell ref="J2:P3"/>
@@ -7989,7 +8284,6 @@
     <mergeCell ref="T30:X30"/>
     <mergeCell ref="T57:X57"/>
     <mergeCell ref="T29:X29"/>
-    <mergeCell ref="B86:AK86"/>
     <mergeCell ref="D53:L53"/>
     <mergeCell ref="D47:L47"/>
     <mergeCell ref="AF59:AK59"/>
@@ -8004,10 +8298,9 @@
     <mergeCell ref="AF26:AK26"/>
     <mergeCell ref="C24:L24"/>
     <mergeCell ref="AD2:AG3"/>
-    <mergeCell ref="D88:AK88"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="Q45:S45"/>
-    <mergeCell ref="B78:I78"/>
+    <mergeCell ref="C99:AK99"/>
     <mergeCell ref="Q32:S32"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="D90:AK90"/>
@@ -8017,6 +8310,7 @@
     <mergeCell ref="T60:X60"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="M36:P36"/>
+    <mergeCell ref="A86:AK86"/>
     <mergeCell ref="Q50:S50"/>
     <mergeCell ref="Y57:AE57"/>
     <mergeCell ref="T42:X42"/>
@@ -8028,21 +8322,22 @@
     <mergeCell ref="T44:X44"/>
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="D55:L55"/>
+    <mergeCell ref="C146:AK146"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="C105:AK105"/>
     <mergeCell ref="D96:AK96"/>
     <mergeCell ref="M31:P31"/>
     <mergeCell ref="Y60:AE60"/>
     <mergeCell ref="N16:AK16"/>
+    <mergeCell ref="B79:I79"/>
+    <mergeCell ref="C149:AK149"/>
     <mergeCell ref="Q55:S55"/>
     <mergeCell ref="Y37:AB37"/>
     <mergeCell ref="C27:L27"/>
-    <mergeCell ref="C67:AK67"/>
+    <mergeCell ref="Q38:S38"/>
     <mergeCell ref="D91:AK91"/>
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="M26:P26"/>
-    <mergeCell ref="B81:I81"/>
-    <mergeCell ref="D106:AK106"/>
     <mergeCell ref="D93:AK93"/>
     <mergeCell ref="AC26:AE26"/>
     <mergeCell ref="Y42:AE42"/>
@@ -8050,14 +8345,15 @@
     <mergeCell ref="AF47:AK47"/>
     <mergeCell ref="M52:P52"/>
     <mergeCell ref="Y58:AE58"/>
+    <mergeCell ref="D109:AK109"/>
     <mergeCell ref="AF46:AK46"/>
     <mergeCell ref="Q53:S53"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
     <mergeCell ref="AF61:AK61"/>
     <mergeCell ref="AF48:AK48"/>
+    <mergeCell ref="B100:AK100"/>
     <mergeCell ref="M28:P28"/>
-    <mergeCell ref="C82:AK82"/>
     <mergeCell ref="M57:P57"/>
     <mergeCell ref="M32:P32"/>
     <mergeCell ref="N18:AK18"/>
@@ -8065,34 +8361,32 @@
     <mergeCell ref="M23:P23"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="AF29:AK29"/>
+    <mergeCell ref="Y38:AB38"/>
     <mergeCell ref="Y24:AB24"/>
-    <mergeCell ref="A39:AK39"/>
-    <mergeCell ref="Q41:S41"/>
     <mergeCell ref="Q1:U1"/>
     <mergeCell ref="AF36:AK36"/>
     <mergeCell ref="Q56:S56"/>
     <mergeCell ref="Q43:S43"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="T31:X31"/>
-    <mergeCell ref="C70:AK70"/>
+    <mergeCell ref="C106:AK106"/>
     <mergeCell ref="M45:P45"/>
-    <mergeCell ref="B75:I75"/>
     <mergeCell ref="D125:AK125"/>
+    <mergeCell ref="AF62:AK62"/>
     <mergeCell ref="M47:P47"/>
     <mergeCell ref="C101:AK101"/>
     <mergeCell ref="N14:AK14"/>
-    <mergeCell ref="D127:AK127"/>
     <mergeCell ref="D114:AK114"/>
     <mergeCell ref="AF51:AK51"/>
     <mergeCell ref="AC22:AE22"/>
     <mergeCell ref="M44:P44"/>
+    <mergeCell ref="AF38:AK38"/>
     <mergeCell ref="M60:P60"/>
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="Y26:AB26"/>
     <mergeCell ref="AF33:AK33"/>
     <mergeCell ref="Q24:S24"/>
     <mergeCell ref="D107:AK107"/>
-    <mergeCell ref="B63:I63"/>
     <mergeCell ref="C36:L36"/>
     <mergeCell ref="Q51:S51"/>
     <mergeCell ref="D52:L52"/>
@@ -8106,14 +8400,13 @@
     <mergeCell ref="AC34:AE34"/>
     <mergeCell ref="M50:P50"/>
     <mergeCell ref="D133:AK133"/>
-    <mergeCell ref="C79:AK79"/>
-    <mergeCell ref="C73:AK73"/>
+    <mergeCell ref="C59:C62"/>
     <mergeCell ref="M55:P55"/>
-    <mergeCell ref="C121:AK121"/>
     <mergeCell ref="M48:P48"/>
     <mergeCell ref="N15:AK15"/>
     <mergeCell ref="D128:AK128"/>
     <mergeCell ref="T23:X23"/>
+    <mergeCell ref="B142:AK142"/>
     <mergeCell ref="Y44:AE44"/>
     <mergeCell ref="D46:L46"/>
     <mergeCell ref="T52:X52"/>
@@ -8121,22 +8414,22 @@
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="T27:X27"/>
     <mergeCell ref="AF54:AK54"/>
-    <mergeCell ref="C43:C56"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="Q26:S26"/>
     <mergeCell ref="T49:X49"/>
+    <mergeCell ref="M38:P38"/>
     <mergeCell ref="AF58:AK58"/>
-    <mergeCell ref="D43:L43"/>
-    <mergeCell ref="C97:AK97"/>
     <mergeCell ref="Y47:AE47"/>
     <mergeCell ref="D123:AK123"/>
     <mergeCell ref="AF60:AK60"/>
-    <mergeCell ref="B99:AK99"/>
+    <mergeCell ref="C58:L58"/>
     <mergeCell ref="AC36:AE36"/>
     <mergeCell ref="Y35:AB35"/>
     <mergeCell ref="D59:L59"/>
     <mergeCell ref="Q37:S37"/>
     <mergeCell ref="Y50:AE50"/>
+    <mergeCell ref="C110:AK110"/>
+    <mergeCell ref="D136:AK136"/>
     <mergeCell ref="Y52:AE52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8310,7 +8603,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/23</t>
+          <t>2026/07/25</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -11509,7 +11802,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/23</t>
+          <t>2026/07/25</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -13929,7 +14222,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/23</t>
+          <t>2026/07/25</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>

--- a/docs/design/ACSMS-SCR-015/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者販売店一括置換画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-015/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者販売店一括置換画面_V1.0.xlsx
@@ -2230,7 +2230,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/25</t>
+          <t>2026/07/29</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2746,7 +2746,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/25</t>
+          <t>2026/07/29</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3675,7 +3675,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/25</t>
+          <t>2026/07/29</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -4236,7 +4236,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/25</t>
+          <t>2026/07/29</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -8442,7 +8442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK129"/>
+  <dimension ref="A1:AK128"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -8603,7 +8603,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/25</t>
+          <t>2026/07/29</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -11090,7 +11090,7 @@
   bank_branch_code, bank_branch_name, hikiotoshi_yokin_shubetsu, hikiotoshi_koza_no, hikiotoshi_koza_meigi,
   dokusyaso_bunrui, nogyosya_bunrui,
   shoki_dokusya_kaishi_date, dokusya_kaishi_date, dokusya_chushi_date, joho_henko_tekiyo_date,
-  seikyu_kaishi_month, biko, henko_riyu,
+  seikyu_kaishi_month, biko,
   saishin_data_flg, zougen_hokoku_flg, shinki_flg, kaiyaku_flg,
   zenkai_hanbaiten_id,
   created_at, created_by
@@ -11109,7 +11109,7 @@
   d.bank_branch_code, d.bank_branch_name, d.hikiotoshi_yokin_shubetsu, d.hikiotoshi_koza_no, d.hikiotoshi_koza_meigi,
   d.dokusyaso_bunrui, d.nogyosya_bunrui,
   d.shoki_dokusya_kaishi_date, d.dokusya_kaishi_date, d.dokusya_chushi_date, :joho_henko_tekiyo_date,
-  d.seikyu_kaishi_month, d.biko, '販売店一括置換',
+  d.seikyu_kaishi_month, d.biko,
   TRUE, TRUE, FALSE, FALSE,
   :zenkai_hanbaiten_id_per_dokusya,
   NOW(), :user_account_id
@@ -11155,47 +11155,40 @@
     <row r="110" ht="18" customHeight="1">
       <c r="C110" s="41" t="inlineStr">
         <is>
-          <t>`henko_riyu`：`'販売店一括置換'` を設定する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="18" customHeight="1">
+          <t>`zougen_hokoku_flg`：販売店変更のため `TRUE`（増減報告対象）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="36" customHeight="1">
       <c r="C111" s="41" t="inlineStr">
         <is>
-          <t>`zougen_hokoku_flg`：販売店変更のため `TRUE`（増減報告対象）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="36" customHeight="1">
+          <t>`zenkai_hanbaiten_id`：更新前の `t_dokusya.hanbaiten_id`（4.3 で取得した値）を設定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="90" customHeight="1">
       <c r="C112" s="41" t="inlineStr">
         <is>
-          <t>`zenkai_hanbaiten_id`：更新前の `t_dokusya.hanbaiten_id`（4.3 で取得した値）を設定する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="90" customHeight="1">
-      <c r="C113" s="41" t="inlineStr">
-        <is>
           <t>`joho_henko_tekiyo_date`：リクエストの `joho_henko_tekiyo_date` を設定する（販売店のみ変更イベント。専用の適用日列は廃止し適用日を joho に一本化・顧客要件 2026-07。UI 編集 Rule2 / SCR-011 §8.1・§14.3 と同一）。マスタ側 `t_dokusya.joho_henko_tekiyo_date` も同日に更新し、最新履歴（saishin）と整合させる。</t>
         </is>
       </c>
     </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="B113" s="27" t="inlineStr">
+        <is>
+          <t>4.6 操作ログ記録</t>
+        </is>
+      </c>
+    </row>
     <row r="114" ht="18" customHeight="1">
-      <c r="B114" s="27" t="inlineStr">
-        <is>
-          <t>4.6 操作ログ記録</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="18" customHeight="1">
-      <c r="C115" s="41" t="inlineStr">
+      <c r="C114" s="41" t="inlineStr">
         <is>
           <t>一括置換操作をバッチ単位で1件記録する（行単位ではなく置換操作1回分）。</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="144" customHeight="1">
-      <c r="C116" s="42" t="inlineStr">
+    <row r="115" ht="144" customHeight="1">
+      <c r="C115" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -11207,64 +11200,64 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D116" s="10" t="n"/>
-      <c r="E116" s="10" t="n"/>
-      <c r="F116" s="10" t="n"/>
-      <c r="G116" s="10" t="n"/>
-      <c r="H116" s="10" t="n"/>
-      <c r="I116" s="10" t="n"/>
-      <c r="J116" s="10" t="n"/>
-      <c r="K116" s="10" t="n"/>
-      <c r="L116" s="10" t="n"/>
-      <c r="M116" s="10" t="n"/>
-      <c r="N116" s="10" t="n"/>
-      <c r="O116" s="10" t="n"/>
-      <c r="P116" s="10" t="n"/>
-      <c r="Q116" s="10" t="n"/>
-      <c r="R116" s="10" t="n"/>
-      <c r="S116" s="10" t="n"/>
-      <c r="T116" s="10" t="n"/>
-      <c r="U116" s="10" t="n"/>
-      <c r="V116" s="10" t="n"/>
-      <c r="W116" s="10" t="n"/>
-      <c r="X116" s="10" t="n"/>
-      <c r="Y116" s="10" t="n"/>
-      <c r="Z116" s="10" t="n"/>
-      <c r="AA116" s="10" t="n"/>
-      <c r="AB116" s="10" t="n"/>
-      <c r="AC116" s="10" t="n"/>
-      <c r="AD116" s="10" t="n"/>
-      <c r="AE116" s="10" t="n"/>
-      <c r="AF116" s="10" t="n"/>
-      <c r="AG116" s="10" t="n"/>
-      <c r="AH116" s="10" t="n"/>
-      <c r="AI116" s="10" t="n"/>
-      <c r="AJ116" s="10" t="n"/>
-      <c r="AK116" s="11" t="n"/>
+      <c r="D115" s="10" t="n"/>
+      <c r="E115" s="10" t="n"/>
+      <c r="F115" s="10" t="n"/>
+      <c r="G115" s="10" t="n"/>
+      <c r="H115" s="10" t="n"/>
+      <c r="I115" s="10" t="n"/>
+      <c r="J115" s="10" t="n"/>
+      <c r="K115" s="10" t="n"/>
+      <c r="L115" s="10" t="n"/>
+      <c r="M115" s="10" t="n"/>
+      <c r="N115" s="10" t="n"/>
+      <c r="O115" s="10" t="n"/>
+      <c r="P115" s="10" t="n"/>
+      <c r="Q115" s="10" t="n"/>
+      <c r="R115" s="10" t="n"/>
+      <c r="S115" s="10" t="n"/>
+      <c r="T115" s="10" t="n"/>
+      <c r="U115" s="10" t="n"/>
+      <c r="V115" s="10" t="n"/>
+      <c r="W115" s="10" t="n"/>
+      <c r="X115" s="10" t="n"/>
+      <c r="Y115" s="10" t="n"/>
+      <c r="Z115" s="10" t="n"/>
+      <c r="AA115" s="10" t="n"/>
+      <c r="AB115" s="10" t="n"/>
+      <c r="AC115" s="10" t="n"/>
+      <c r="AD115" s="10" t="n"/>
+      <c r="AE115" s="10" t="n"/>
+      <c r="AF115" s="10" t="n"/>
+      <c r="AG115" s="10" t="n"/>
+      <c r="AH115" s="10" t="n"/>
+      <c r="AI115" s="10" t="n"/>
+      <c r="AJ115" s="10" t="n"/>
+      <c r="AK115" s="11" t="n"/>
+    </row>
+    <row r="116" ht="54" customHeight="1">
+      <c r="C116" s="41" t="inlineStr">
+        <is>
+          <t>`before_value`：置換前データのサマリ JSON `{ "dokusya_ids": [...], "previous_hanbaiten_ids": {dokusya_id: hanbaiten_id, ...} }`</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="54" customHeight="1">
       <c r="C117" s="41" t="inlineStr">
         <is>
-          <t>`before_value`：置換前データのサマリ JSON `{ "dokusya_ids": [...], "previous_hanbaiten_ids": {dokusya_id: hanbaiten_id, ...} }`</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="54" customHeight="1">
+          <t>`after_value`：置換結果サマリ JSON `{ "total_count", "new_hanbaiten_id", "joho_henko_tekiyo_date", "rireki_count" }`</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="18" customHeight="1">
       <c r="C118" s="41" t="inlineStr">
         <is>
-          <t>`after_value`：置換結果サマリ JSON `{ "total_count", "new_hanbaiten_id", "joho_henko_tekiyo_date", "rireki_count" }`</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="18" customHeight="1">
-      <c r="C119" s="41" t="inlineStr">
-        <is>
           <t>パスワード等の機密情報は含めないこと。</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="144" customHeight="1">
-      <c r="C120" s="42" t="inlineStr">
+    <row r="119" ht="144" customHeight="1">
+      <c r="C119" s="42" t="inlineStr">
         <is>
           <t>{
   "total_count": 3,
@@ -11276,99 +11269,99 @@
 }</t>
         </is>
       </c>
-      <c r="D120" s="10" t="n"/>
-      <c r="E120" s="10" t="n"/>
-      <c r="F120" s="10" t="n"/>
-      <c r="G120" s="10" t="n"/>
-      <c r="H120" s="10" t="n"/>
-      <c r="I120" s="10" t="n"/>
-      <c r="J120" s="10" t="n"/>
-      <c r="K120" s="10" t="n"/>
-      <c r="L120" s="10" t="n"/>
-      <c r="M120" s="10" t="n"/>
-      <c r="N120" s="10" t="n"/>
-      <c r="O120" s="10" t="n"/>
-      <c r="P120" s="10" t="n"/>
-      <c r="Q120" s="10" t="n"/>
-      <c r="R120" s="10" t="n"/>
-      <c r="S120" s="10" t="n"/>
-      <c r="T120" s="10" t="n"/>
-      <c r="U120" s="10" t="n"/>
-      <c r="V120" s="10" t="n"/>
-      <c r="W120" s="10" t="n"/>
-      <c r="X120" s="10" t="n"/>
-      <c r="Y120" s="10" t="n"/>
-      <c r="Z120" s="10" t="n"/>
-      <c r="AA120" s="10" t="n"/>
-      <c r="AB120" s="10" t="n"/>
-      <c r="AC120" s="10" t="n"/>
-      <c r="AD120" s="10" t="n"/>
-      <c r="AE120" s="10" t="n"/>
-      <c r="AF120" s="10" t="n"/>
-      <c r="AG120" s="10" t="n"/>
-      <c r="AH120" s="10" t="n"/>
-      <c r="AI120" s="10" t="n"/>
-      <c r="AJ120" s="10" t="n"/>
-      <c r="AK120" s="11" t="n"/>
+      <c r="D119" s="10" t="n"/>
+      <c r="E119" s="10" t="n"/>
+      <c r="F119" s="10" t="n"/>
+      <c r="G119" s="10" t="n"/>
+      <c r="H119" s="10" t="n"/>
+      <c r="I119" s="10" t="n"/>
+      <c r="J119" s="10" t="n"/>
+      <c r="K119" s="10" t="n"/>
+      <c r="L119" s="10" t="n"/>
+      <c r="M119" s="10" t="n"/>
+      <c r="N119" s="10" t="n"/>
+      <c r="O119" s="10" t="n"/>
+      <c r="P119" s="10" t="n"/>
+      <c r="Q119" s="10" t="n"/>
+      <c r="R119" s="10" t="n"/>
+      <c r="S119" s="10" t="n"/>
+      <c r="T119" s="10" t="n"/>
+      <c r="U119" s="10" t="n"/>
+      <c r="V119" s="10" t="n"/>
+      <c r="W119" s="10" t="n"/>
+      <c r="X119" s="10" t="n"/>
+      <c r="Y119" s="10" t="n"/>
+      <c r="Z119" s="10" t="n"/>
+      <c r="AA119" s="10" t="n"/>
+      <c r="AB119" s="10" t="n"/>
+      <c r="AC119" s="10" t="n"/>
+      <c r="AD119" s="10" t="n"/>
+      <c r="AE119" s="10" t="n"/>
+      <c r="AF119" s="10" t="n"/>
+      <c r="AG119" s="10" t="n"/>
+      <c r="AH119" s="10" t="n"/>
+      <c r="AI119" s="10" t="n"/>
+      <c r="AJ119" s="10" t="n"/>
+      <c r="AK119" s="11" t="n"/>
+    </row>
+    <row r="120" ht="18" customHeight="1">
+      <c r="B120" s="27" t="inlineStr">
+        <is>
+          <t>4.7 レスポンス生成</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="18" customHeight="1">
-      <c r="B121" s="27" t="inlineStr">
-        <is>
-          <t>4.7 レスポンス生成</t>
+      <c r="C121" s="41" t="inlineStr">
+        <is>
+          <t>トランザクションをコミットする。</t>
         </is>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
       <c r="C122" s="41" t="inlineStr">
         <is>
-          <t>トランザクションをコミットする。</t>
+          <t>置換結果サマリを `data` オブジェクトとして返却する。HTTP 200。</t>
         </is>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
       <c r="C123" s="41" t="inlineStr">
         <is>
-          <t>置換結果サマリを `data` オブジェクトとして返却する。HTTP 200。</t>
+          <t>`message`：`置換処理が完了しました。`（ACSMS-MSG-015-008）</t>
         </is>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
-      <c r="C124" s="41" t="inlineStr">
-        <is>
-          <t>`message`：`置換処理が完了しました。`（ACSMS-MSG-015-008）</t>
+      <c r="B124" s="27" t="inlineStr">
+        <is>
+          <t>4.8 例外処理</t>
         </is>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
-      <c r="B125" s="27" t="inlineStr">
-        <is>
-          <t>4.8 例外処理</t>
+      <c r="C125" s="41" t="inlineStr">
+        <is>
+          <t>置換処理中にエラーが発生した場合、トランザクションを全件ロールバックする。</t>
         </is>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
       <c r="C126" s="41" t="inlineStr">
         <is>
-          <t>置換処理中にエラーが発生した場合、トランザクションを全件ロールバックする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="18" customHeight="1">
+          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="36" customHeight="1">
       <c r="C127" s="41" t="inlineStr">
         <is>
-          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="36" customHeight="1">
-      <c r="C128" s="41" t="inlineStr">
-        <is>
           <t>エラー発生時もエラーログを記録する（`log_type = 3`）。**トランザクション外で別途記録する**。</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="144" customHeight="1">
-      <c r="C129" s="42" t="inlineStr">
+    <row r="128" ht="144" customHeight="1">
+      <c r="C128" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -11380,43 +11373,43 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D129" s="10" t="n"/>
-      <c r="E129" s="10" t="n"/>
-      <c r="F129" s="10" t="n"/>
-      <c r="G129" s="10" t="n"/>
-      <c r="H129" s="10" t="n"/>
-      <c r="I129" s="10" t="n"/>
-      <c r="J129" s="10" t="n"/>
-      <c r="K129" s="10" t="n"/>
-      <c r="L129" s="10" t="n"/>
-      <c r="M129" s="10" t="n"/>
-      <c r="N129" s="10" t="n"/>
-      <c r="O129" s="10" t="n"/>
-      <c r="P129" s="10" t="n"/>
-      <c r="Q129" s="10" t="n"/>
-      <c r="R129" s="10" t="n"/>
-      <c r="S129" s="10" t="n"/>
-      <c r="T129" s="10" t="n"/>
-      <c r="U129" s="10" t="n"/>
-      <c r="V129" s="10" t="n"/>
-      <c r="W129" s="10" t="n"/>
-      <c r="X129" s="10" t="n"/>
-      <c r="Y129" s="10" t="n"/>
-      <c r="Z129" s="10" t="n"/>
-      <c r="AA129" s="10" t="n"/>
-      <c r="AB129" s="10" t="n"/>
-      <c r="AC129" s="10" t="n"/>
-      <c r="AD129" s="10" t="n"/>
-      <c r="AE129" s="10" t="n"/>
-      <c r="AF129" s="10" t="n"/>
-      <c r="AG129" s="10" t="n"/>
-      <c r="AH129" s="10" t="n"/>
-      <c r="AI129" s="10" t="n"/>
-      <c r="AJ129" s="10" t="n"/>
-      <c r="AK129" s="11" t="n"/>
+      <c r="D128" s="10" t="n"/>
+      <c r="E128" s="10" t="n"/>
+      <c r="F128" s="10" t="n"/>
+      <c r="G128" s="10" t="n"/>
+      <c r="H128" s="10" t="n"/>
+      <c r="I128" s="10" t="n"/>
+      <c r="J128" s="10" t="n"/>
+      <c r="K128" s="10" t="n"/>
+      <c r="L128" s="10" t="n"/>
+      <c r="M128" s="10" t="n"/>
+      <c r="N128" s="10" t="n"/>
+      <c r="O128" s="10" t="n"/>
+      <c r="P128" s="10" t="n"/>
+      <c r="Q128" s="10" t="n"/>
+      <c r="R128" s="10" t="n"/>
+      <c r="S128" s="10" t="n"/>
+      <c r="T128" s="10" t="n"/>
+      <c r="U128" s="10" t="n"/>
+      <c r="V128" s="10" t="n"/>
+      <c r="W128" s="10" t="n"/>
+      <c r="X128" s="10" t="n"/>
+      <c r="Y128" s="10" t="n"/>
+      <c r="Z128" s="10" t="n"/>
+      <c r="AA128" s="10" t="n"/>
+      <c r="AB128" s="10" t="n"/>
+      <c r="AC128" s="10" t="n"/>
+      <c r="AD128" s="10" t="n"/>
+      <c r="AE128" s="10" t="n"/>
+      <c r="AF128" s="10" t="n"/>
+      <c r="AG128" s="10" t="n"/>
+      <c r="AH128" s="10" t="n"/>
+      <c r="AI128" s="10" t="n"/>
+      <c r="AJ128" s="10" t="n"/>
+      <c r="AK128" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="213">
+  <mergeCells count="212">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Y28:AB28"/>
     <mergeCell ref="C57:AK57"/>
@@ -11444,7 +11437,6 @@
     <mergeCell ref="C45:AK45"/>
     <mergeCell ref="AF23:AK23"/>
     <mergeCell ref="C128:AK128"/>
-    <mergeCell ref="C113:AK113"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="N19:AK19"/>
     <mergeCell ref="J19:M19"/>
@@ -11462,13 +11454,12 @@
     <mergeCell ref="C127:AK127"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="M35:P35"/>
+    <mergeCell ref="C114:AK114"/>
     <mergeCell ref="AF36:AK36"/>
-    <mergeCell ref="C129:AK129"/>
     <mergeCell ref="Q25:S25"/>
     <mergeCell ref="D35:L35"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="B65:I65"/>
-    <mergeCell ref="B114:AK114"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="AF34:AK34"/>
     <mergeCell ref="C51:AK51"/>
@@ -11482,6 +11473,7 @@
     <mergeCell ref="T28:X28"/>
     <mergeCell ref="C48:AK48"/>
     <mergeCell ref="B91:AK91"/>
+    <mergeCell ref="B113:AK113"/>
     <mergeCell ref="T37:X37"/>
     <mergeCell ref="C106:AK106"/>
     <mergeCell ref="Y25:AB25"/>
@@ -11541,6 +11533,7 @@
     <mergeCell ref="Y37:AE37"/>
     <mergeCell ref="T39:X39"/>
     <mergeCell ref="C81:AK81"/>
+    <mergeCell ref="C125:AK125"/>
     <mergeCell ref="Y27:AB27"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="J7:AK7"/>
@@ -11567,6 +11560,7 @@
     <mergeCell ref="C63:AK63"/>
     <mergeCell ref="M39:P39"/>
     <mergeCell ref="C34:C38"/>
+    <mergeCell ref="C121:AK121"/>
     <mergeCell ref="C93:AK93"/>
     <mergeCell ref="T26:X26"/>
     <mergeCell ref="J10:AK10"/>
@@ -11578,18 +11572,15 @@
     <mergeCell ref="C105:AK105"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="AH1:AK1"/>
-    <mergeCell ref="C120:AK120"/>
     <mergeCell ref="C119:AK119"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="T27:X27"/>
-    <mergeCell ref="B125:AK125"/>
     <mergeCell ref="T36:X36"/>
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="Q38:S38"/>
     <mergeCell ref="D97:AK97"/>
-    <mergeCell ref="B121:AK121"/>
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="M26:P26"/>
@@ -11602,6 +11593,7 @@
     <mergeCell ref="AC26:AE26"/>
     <mergeCell ref="T35:X35"/>
     <mergeCell ref="C92:AK92"/>
+    <mergeCell ref="B120:AK120"/>
     <mergeCell ref="Y23:AB23"/>
     <mergeCell ref="Y32:AE32"/>
     <mergeCell ref="T25:X25"/>
@@ -11614,9 +11606,9 @@
     <mergeCell ref="B53:I53"/>
     <mergeCell ref="B74:AK74"/>
     <mergeCell ref="B83:AK83"/>
-    <mergeCell ref="C124:AK124"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="J15:M15"/>
+    <mergeCell ref="B124:AK124"/>
     <mergeCell ref="AD1:AG1"/>
     <mergeCell ref="C90:AK90"/>
     <mergeCell ref="AF39:AK39"/>
@@ -11802,7 +11794,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/25</t>
+          <t>2026/07/29</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -14222,7 +14214,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/25</t>
+          <t>2026/07/29</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>

--- a/docs/design/ACSMS-SCR-015/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者販売店一括置換画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-015/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者販売店一括置換画面_V1.0.xlsx
@@ -2230,7 +2230,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/29</t>
+          <t>2026/08/03</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2746,7 +2746,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/29</t>
+          <t>2026/08/03</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3675,7 +3675,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/29</t>
+          <t>2026/08/03</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -4236,7 +4236,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/29</t>
+          <t>2026/08/03</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -6587,7 +6587,7 @@
       <c r="X53" s="11" t="n"/>
       <c r="Y53" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z53" s="10" t="n"/>
@@ -6598,7 +6598,7 @@
       <c r="AE53" s="11" t="n"/>
       <c r="AF53" s="19" t="inlineStr">
         <is>
-          <t>販売店ID</t>
+          <t>販売店ID※未設定(NULL)あり</t>
         </is>
       </c>
       <c r="AG53" s="10" t="n"/>
@@ -8603,7 +8603,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/29</t>
+          <t>2026/08/03</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -11794,7 +11794,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/29</t>
+          <t>2026/08/03</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -14214,7 +14214,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/29</t>
+          <t>2026/08/03</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -15267,7 +15267,7 @@
       <c r="X31" s="11" t="n"/>
       <c r="Y31" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z31" s="10" t="n"/>
@@ -15278,7 +15278,7 @@
       <c r="AE31" s="11" t="n"/>
       <c r="AF31" s="19" t="inlineStr">
         <is>
-          <t>販売店ID</t>
+          <t>販売店ID※未設定(NULL)あり</t>
         </is>
       </c>
       <c r="AG31" s="10" t="n"/>
